--- a/수정된 사양서/프로젝트 사양서.xlsx
+++ b/수정된 사양서/프로젝트 사양서.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504BB6C7-59B8-4D3A-8D48-41C9047064F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704AFFF3-9349-491C-9449-B025D442787F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAY-1(한글)" sheetId="10" r:id="rId1"/>
     <sheet name="DAY-2(한글)" sheetId="11" r:id="rId2"/>
-    <sheet name="DAY-2" sheetId="2" r:id="rId3"/>
+    <sheet name="Day-3(한글)" sheetId="12" r:id="rId3"/>
     <sheet name="Day-3" sheetId="3" r:id="rId4"/>
     <sheet name="DAY-4" sheetId="4" r:id="rId5"/>
     <sheet name="DAY-5" sheetId="5" r:id="rId6"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="520">
   <si>
     <t>12v</t>
   </si>
@@ -49,75 +49,6 @@
   </si>
   <si>
     <t>CH340C</t>
-  </si>
-  <si>
-    <t>STM32F103</t>
-  </si>
-  <si>
-    <t>Page-11</t>
-  </si>
-  <si>
-    <t>Block Diag</t>
-  </si>
-  <si>
-    <t>Page- 15</t>
-  </si>
-  <si>
-    <t>Booting Config</t>
-  </si>
-  <si>
-    <t>Page-26</t>
-  </si>
-  <si>
-    <t>PIN Names, Package info</t>
-  </si>
-  <si>
-    <t>28-33</t>
-  </si>
-  <si>
-    <t>Pin Config Table</t>
-  </si>
-  <si>
-    <t>Page-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load Cap, VDD </t>
-  </si>
-  <si>
-    <t>Page-36</t>
-  </si>
-  <si>
-    <t>Voltage Page</t>
-  </si>
-  <si>
-    <t>Page-37</t>
-  </si>
-  <si>
-    <t>Max Power Est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page-51 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page-60 </t>
-  </si>
-  <si>
-    <t>ESD Table</t>
-  </si>
-  <si>
-    <t>Page-68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset </t>
-  </si>
-  <si>
-    <t>Page-70</t>
-  </si>
-  <si>
-    <t>I2C Pull-ups</t>
-  </si>
-  <si>
-    <t>Page-78</t>
   </si>
   <si>
     <t>Design Guidelines</t>
@@ -1801,6 +1732,184 @@
   </si>
   <si>
     <t>가이드라인 제시</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>누설전류</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작전압</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break down 전압</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>클램핑 전압</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기생 커패시턴스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3V보다 클 때</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>용량성 리액턴스(Xc)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/(2*pi*C)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작전압에 가까울 수록 좋음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESD Diode/Ferrite Bead 선정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을수록 좋음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구사항</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 부품</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESD3V3D9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력 소모량에 영향</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU 공급 전압에 따름</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3V보다 클 때와 반응속도가 빨라야함</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU공급 전압이 3.3V이므로</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>고주파에서 GND로 가며, 신호 감쇠 영향</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방향성</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>단방향</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0~3.3V이므로</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>G8X-188S7-BP</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45 Magnetic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>절연상태(내부 Trans 사용)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>100Mbps 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구사항 2MByte/s</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clamping 전압은
+MCU의 Absoulte maximum voltage 보다
+낮은게 좋긴 하다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MPZ1608B471ATA00</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rdc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>높을수록 좋음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>원하는 주파수에서의 임피던스 확인 필</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작 전류보다 낮으면 발열/소손 예상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구 주파수 내</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>비드는 노이즈를 확인하고
+특정 주파수 라인 제거를 목적
+(Knee Freq 확인 필)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>낮을수록 좋음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>높으면 전압 강하를 일으킴</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>원하는 주파수 내에서만 높아야함</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethernet PHY TX+, TX-, RX+, RX- 라인당 전류</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>JTAG과 SWD는
+선택사항</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Programming / debugging</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SWD -&gt; 프로그램, 디버깅, ARM 아키텍쳐, printf 가능
+JTAG -&gt; Test, 독립적, 별도의 아키텍쳐 없음</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2329,7 +2438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2426,6 +2535,113 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2443,122 +2659,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2854,1386 +2965,1352 @@
   <sheetData>
     <row r="2" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="3" spans="2:9">
-      <c r="B3" s="72" t="s">
-        <v>369</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
+      <c r="B3" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B4" s="73"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="59"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
     </row>
     <row r="5" spans="2:9" ht="17.25" thickBot="1">
       <c r="B5" s="29" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="F5" s="74" t="s">
-        <v>256</v>
-      </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="75"/>
+        <v>235</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="76" t="s">
-        <v>362</v>
+      <c r="B6" s="57" t="s">
+        <v>339</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="44"/>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="41"/>
+      <c r="C7" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="48"/>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="41"/>
+      <c r="C8" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="48"/>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="41"/>
+      <c r="C9" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="41"/>
+      <c r="C10" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="48"/>
+    </row>
+    <row r="11" spans="2:9" ht="33">
+      <c r="B11" s="41"/>
+      <c r="C11" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="48"/>
+    </row>
+    <row r="12" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B12" s="42"/>
+      <c r="C12" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
+    </row>
+    <row r="14" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B14" s="42"/>
+      <c r="C14" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46"/>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="44"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="41"/>
+      <c r="C16" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="48"/>
+    </row>
+    <row r="17" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B17" s="42"/>
+      <c r="C17" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="46"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="44"/>
-      <c r="C7" s="23" t="s">
+      <c r="D18" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="44"/>
+    </row>
+    <row r="19" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B19" s="42"/>
+      <c r="C19" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="49"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="44"/>
-      <c r="C8" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="49"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="44"/>
-      <c r="C9" s="23" t="s">
+      <c r="D19" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="49"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="44"/>
-      <c r="C10" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="49"/>
-    </row>
-    <row r="11" spans="2:9" ht="33">
-      <c r="B11" s="44"/>
-      <c r="C11" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>365</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="49"/>
-    </row>
-    <row r="12" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B12" s="45"/>
-      <c r="C12" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>366</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="51"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="76" t="s">
-        <v>359</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47"/>
-    </row>
-    <row r="14" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B14" s="45"/>
-      <c r="C14" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="51"/>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="44"/>
-      <c r="C16" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>376</v>
-      </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="49"/>
-    </row>
-    <row r="17" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B17" s="45"/>
-      <c r="C17" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="47"/>
-    </row>
-    <row r="19" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B19" s="45"/>
-      <c r="C19" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="46"/>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="26" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>405</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>406</v>
-      </c>
-      <c r="F20" s="66" t="s">
-        <v>280</v>
-      </c>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
+        <v>255</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>383</v>
+      </c>
+      <c r="F20" s="61" t="s">
+        <v>257</v>
+      </c>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="28" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="69"/>
+        <v>256</v>
+      </c>
+      <c r="D21" s="59"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="64"/>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="28" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="69"/>
+        <v>258</v>
+      </c>
+      <c r="D22" s="59"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="64"/>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="28" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="69"/>
+        <v>259</v>
+      </c>
+      <c r="D23" s="59"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="64"/>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="28" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="69"/>
+        <v>264</v>
+      </c>
+      <c r="D24" s="59"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="64"/>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="28" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="69"/>
+        <v>266</v>
+      </c>
+      <c r="D25" s="59"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="64"/>
     </row>
     <row r="26" spans="2:9" ht="17.25" thickBot="1">
       <c r="B26" s="27" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="D26" s="65"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="71"/>
+        <v>268</v>
+      </c>
+      <c r="D26" s="60"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="66"/>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="26" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="54"/>
+        <v>412</v>
+      </c>
+      <c r="F27" s="67"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="51"/>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="28" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="F28" s="55"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="56"/>
+        <v>349</v>
+      </c>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="70"/>
     </row>
     <row r="29" spans="2:9" ht="17.25" thickBot="1">
       <c r="B29" s="27" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="59"/>
+        <v>349</v>
+      </c>
+      <c r="F29" s="71"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="54"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="43" t="s">
-        <v>296</v>
+      <c r="B30" s="40" t="s">
+        <v>273</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="D30" s="32">
         <v>24</v>
       </c>
-      <c r="E30" s="38" t="s">
-        <v>436</v>
-      </c>
-      <c r="F30" s="52"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="54"/>
+      <c r="E30" s="75" t="s">
+        <v>413</v>
+      </c>
+      <c r="F30" s="67"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="51"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="44"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="23" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E31" s="39"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="56"/>
+        <v>284</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="44"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="23" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="D32" s="21">
         <v>128</v>
       </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="56"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="70"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="44"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="23" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="56"/>
+        <v>279</v>
+      </c>
+      <c r="E33" s="76"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="70"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B34" s="45"/>
+      <c r="B34" s="42"/>
       <c r="C34" s="24" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="59"/>
+        <v>281</v>
+      </c>
+      <c r="E34" s="77"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="54"/>
     </row>
     <row r="35" spans="2:9" ht="17.25" thickBot="1">
       <c r="B35" s="29" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="F35" s="60"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="62"/>
+        <v>412</v>
+      </c>
+      <c r="F35" s="72"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="74"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="43" t="s">
-        <v>308</v>
+      <c r="B36" s="40" t="s">
+        <v>285</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="E36" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="47"/>
+        <v>286</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="44"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="44"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="23" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="49"/>
+        <v>284</v>
+      </c>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="48"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="44"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="23" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="D38" s="21">
         <f>5000/0.005</f>
         <v>1000000</v>
       </c>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="49"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="48"/>
     </row>
     <row r="39" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B39" s="45"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="46"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="40" t="s">
+        <v>385</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="75" t="s">
+        <v>414</v>
+      </c>
+      <c r="F40" s="67"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="51"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="41"/>
+      <c r="C41" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E41" s="76"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="70"/>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="41"/>
+      <c r="C42" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="E42" s="76"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="70"/>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="41"/>
+      <c r="C43" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="E43" s="76"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="70"/>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="41"/>
+      <c r="C44" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="E44" s="76"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="70"/>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="41"/>
+      <c r="C45" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E45" s="76"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="70"/>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="41"/>
+      <c r="C46" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E46" s="76"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="70"/>
+    </row>
+    <row r="47" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B47" s="42"/>
+      <c r="C47" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E47" s="77"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="54"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="E48" s="78" t="s">
+        <v>412</v>
+      </c>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="44"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="41"/>
+      <c r="C49" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="E49" s="76"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="48"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="41"/>
+      <c r="C50" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E50" s="76"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="48"/>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="41"/>
+      <c r="C51" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="E51" s="76"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="48"/>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="41"/>
+      <c r="C52" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E52" s="76"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="48"/>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" s="41"/>
+      <c r="C53" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="E53" s="76"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="48"/>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" s="41"/>
+      <c r="C54" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D54" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="51"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="43" t="s">
-        <v>408</v>
-      </c>
-      <c r="C40" s="19" t="s">
+      <c r="E54" s="76"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="48"/>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="41"/>
+      <c r="C55" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>437</v>
-      </c>
-      <c r="F40" s="52"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="54"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="44"/>
-      <c r="C41" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="D41" s="21" t="s">
+      <c r="E55" s="76"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="48"/>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="41"/>
+      <c r="C56" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="E56" s="76"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="48"/>
+    </row>
+    <row r="57" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B57" s="42"/>
+      <c r="C57" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E57" s="77"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="46"/>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" s="40" t="s">
+        <v>321</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="E58" s="78" t="s">
+        <v>412</v>
+      </c>
+      <c r="F58" s="67"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="51"/>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" s="41"/>
+      <c r="C59" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E59" s="76"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="70"/>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" s="41"/>
+      <c r="C60" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E60" s="76"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="69"/>
+      <c r="H60" s="69"/>
+      <c r="I60" s="70"/>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="41"/>
+      <c r="C61" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E61" s="76"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="70"/>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" s="41"/>
+      <c r="C62" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E62" s="76"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="69"/>
+      <c r="I62" s="70"/>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="B63" s="41"/>
+      <c r="C63" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="E63" s="76"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="70"/>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" s="41"/>
+      <c r="C64" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="E64" s="76"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="70"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="41"/>
+      <c r="C65" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="70"/>
+    </row>
+    <row r="66" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B66" s="42"/>
+      <c r="C66" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="34"/>
+      <c r="E66" s="77"/>
+      <c r="F66" s="71"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="54"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="E67" s="78"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="51"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="B68" s="41"/>
+      <c r="C68" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="76"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="70"/>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" s="41"/>
+      <c r="C69" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="E69" s="76"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="69"/>
+      <c r="H69" s="69"/>
+      <c r="I69" s="70"/>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="B70" s="41"/>
+      <c r="C70" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E70" s="76"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="69"/>
+      <c r="I70" s="70"/>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="B71" s="41"/>
+      <c r="C71" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" s="76"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="69"/>
+      <c r="H71" s="69"/>
+      <c r="I71" s="70"/>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="B72" s="41"/>
+      <c r="C72" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E72" s="76"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="69"/>
+      <c r="H72" s="69"/>
+      <c r="I72" s="70"/>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="41"/>
+      <c r="C73" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="E73" s="76"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="69"/>
+      <c r="H73" s="69"/>
+      <c r="I73" s="70"/>
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="41"/>
+      <c r="C74" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E74" s="76"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="69"/>
+      <c r="I74" s="70"/>
+    </row>
+    <row r="75" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B75" s="42"/>
+      <c r="C75" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="D75" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="56"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="44"/>
-      <c r="C42" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="E42" s="39"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="56"/>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="44"/>
-      <c r="C43" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="E43" s="39"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="56"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="44"/>
-      <c r="C44" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="E44" s="39"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="56"/>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="44"/>
-      <c r="C45" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="E45" s="39"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="56"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="44"/>
-      <c r="C46" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="E46" s="39"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="56"/>
-    </row>
-    <row r="47" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B47" s="45"/>
-      <c r="C47" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="D47" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E47" s="40"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="43" t="s">
-        <v>326</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="E48" s="41" t="s">
-        <v>435</v>
-      </c>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="47"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="44"/>
-      <c r="C49" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E49" s="39"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="49"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="44"/>
-      <c r="C50" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="E50" s="39"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="49"/>
-    </row>
-    <row r="51" spans="2:9">
-      <c r="B51" s="44"/>
-      <c r="C51" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="49"/>
-    </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="44"/>
-      <c r="C52" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="E52" s="39"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="49"/>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" s="44"/>
-      <c r="C53" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="E53" s="39"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="49"/>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" s="44"/>
-      <c r="C54" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="E54" s="39"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="49"/>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="44"/>
-      <c r="C55" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="E55" s="39"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="49"/>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" s="44"/>
-      <c r="C56" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="E56" s="39"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="49"/>
-    </row>
-    <row r="57" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B57" s="45"/>
-      <c r="C57" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="51"/>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" s="43" t="s">
-        <v>344</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="E58" s="41" t="s">
-        <v>435</v>
-      </c>
-      <c r="F58" s="52"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="54"/>
-    </row>
-    <row r="59" spans="2:9">
-      <c r="B59" s="44"/>
-      <c r="C59" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="55"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="56"/>
-    </row>
-    <row r="60" spans="2:9">
-      <c r="B60" s="44"/>
-      <c r="C60" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="E60" s="39"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="56"/>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="B61" s="44"/>
-      <c r="C61" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="E61" s="39"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="56"/>
-    </row>
-    <row r="62" spans="2:9">
-      <c r="B62" s="44"/>
-      <c r="C62" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="E62" s="39"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="56"/>
-    </row>
-    <row r="63" spans="2:9">
-      <c r="B63" s="44"/>
-      <c r="C63" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="E63" s="39"/>
-      <c r="F63" s="55"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="56"/>
-    </row>
-    <row r="64" spans="2:9">
-      <c r="B64" s="44"/>
-      <c r="C64" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="E64" s="39"/>
-      <c r="F64" s="55"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="56"/>
-    </row>
-    <row r="65" spans="2:9">
-      <c r="B65" s="44"/>
-      <c r="C65" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="D65" s="21"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="55"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="56"/>
-    </row>
-    <row r="66" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B66" s="45"/>
-      <c r="C66" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="D66" s="34"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="59"/>
-    </row>
-    <row r="67" spans="2:9">
-      <c r="B67" s="43" t="s">
-        <v>378</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D67" s="32" t="s">
-        <v>379</v>
-      </c>
-      <c r="E67" s="41"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="54"/>
-    </row>
-    <row r="68" spans="2:9">
-      <c r="B68" s="44"/>
-      <c r="C68" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E68" s="39"/>
-      <c r="F68" s="55"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="56"/>
-    </row>
-    <row r="69" spans="2:9">
-      <c r="B69" s="44"/>
-      <c r="C69" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="E69" s="39"/>
-      <c r="F69" s="55"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="56"/>
-    </row>
-    <row r="70" spans="2:9">
-      <c r="B70" s="44"/>
-      <c r="C70" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="E70" s="39"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="56"/>
-    </row>
-    <row r="71" spans="2:9">
-      <c r="B71" s="44"/>
-      <c r="C71" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="E71" s="39"/>
-      <c r="F71" s="55"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="56"/>
-    </row>
-    <row r="72" spans="2:9">
-      <c r="B72" s="44"/>
-      <c r="C72" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="E72" s="39"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="56"/>
-    </row>
-    <row r="73" spans="2:9">
-      <c r="B73" s="44"/>
-      <c r="C73" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>439</v>
-      </c>
-      <c r="E73" s="39"/>
-      <c r="F73" s="55"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="56"/>
-    </row>
-    <row r="74" spans="2:9">
-      <c r="B74" s="44"/>
-      <c r="C74" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="56"/>
-    </row>
-    <row r="75" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B75" s="45"/>
-      <c r="C75" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="D75" s="34" t="s">
-        <v>391</v>
-      </c>
-      <c r="E75" s="40"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58"/>
-      <c r="I75" s="59"/>
+      <c r="E75" s="77"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="54"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="36" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
+        <v>391</v>
+      </c>
+      <c r="F77" s="69" t="s">
+        <v>402</v>
+      </c>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="16" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="C78" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="F78" s="69" t="s">
         <v>393</v>
       </c>
-      <c r="D78" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="E78" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>416</v>
-      </c>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="69"/>
+      <c r="I78" s="69"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E79" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="F79" s="69" t="s">
         <v>395</v>
       </c>
-      <c r="D79" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="F79" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
+      <c r="G79" s="69"/>
+      <c r="H79" s="69"/>
+      <c r="I79" s="69"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="16" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>420</v>
-      </c>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
+        <v>396</v>
+      </c>
+      <c r="F80" s="69" t="s">
+        <v>397</v>
+      </c>
+      <c r="G80" s="69"/>
+      <c r="H80" s="69"/>
+      <c r="I80" s="69"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="D81" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="E81" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="D81" s="16" t="s">
-        <v>421</v>
-      </c>
-      <c r="E81" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="G81" s="37"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37"/>
+      <c r="F81" s="69" t="s">
+        <v>400</v>
+      </c>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="16" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="C82" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="F82" s="79" t="s">
         <v>401</v>
       </c>
-      <c r="D82" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="E82" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="F82" s="42" t="s">
-        <v>424</v>
-      </c>
-      <c r="G82" s="37"/>
-      <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
+      <c r="G82" s="69"/>
+      <c r="H82" s="69"/>
+      <c r="I82" s="69"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="16" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>427</v>
-      </c>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
+        <v>405</v>
+      </c>
+      <c r="F83" s="69" t="s">
+        <v>404</v>
+      </c>
+      <c r="G83" s="69"/>
+      <c r="H83" s="69"/>
+      <c r="I83" s="69"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="16" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>433</v>
-      </c>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
+        <v>409</v>
+      </c>
+      <c r="F84" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="G84" s="69"/>
+      <c r="H84" s="69"/>
+      <c r="I84" s="69"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="16" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>447</v>
-      </c>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
+        <v>425</v>
+      </c>
+      <c r="F85" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="G85" s="69"/>
+      <c r="H85" s="69"/>
+      <c r="I85" s="69"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="16" t="s">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>440</v>
-      </c>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+        <v>408</v>
+      </c>
+      <c r="F86" s="69" t="s">
+        <v>417</v>
+      </c>
+      <c r="G86" s="69"/>
+      <c r="H86" s="69"/>
+      <c r="I86" s="69"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="16" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+        <v>408</v>
+      </c>
+      <c r="F87" s="69" t="s">
+        <v>420</v>
+      </c>
+      <c r="G87" s="69"/>
+      <c r="H87" s="69"/>
+      <c r="I87" s="69"/>
     </row>
     <row r="88" spans="2:9">
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="F88" s="69"/>
+      <c r="G88" s="69"/>
+      <c r="H88" s="69"/>
+      <c r="I88" s="69"/>
     </row>
     <row r="89" spans="2:9">
-      <c r="F89" s="37"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="69"/>
+      <c r="H89" s="69"/>
+      <c r="I89" s="69"/>
     </row>
     <row r="90" spans="2:9">
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
+      <c r="F90" s="69"/>
+      <c r="G90" s="69"/>
+      <c r="H90" s="69"/>
+      <c r="I90" s="69"/>
     </row>
     <row r="91" spans="2:9">
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
+      <c r="F91" s="69"/>
+      <c r="G91" s="69"/>
+      <c r="H91" s="69"/>
+      <c r="I91" s="69"/>
     </row>
     <row r="92" spans="2:9">
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="69"/>
+      <c r="H92" s="69"/>
+      <c r="I92" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="F13:I14"/>
-    <mergeCell ref="F15:I17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:I19"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="F6:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D20:D26"/>
-    <mergeCell ref="E20:E26"/>
-    <mergeCell ref="F20:I26"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="F30:I34"/>
-    <mergeCell ref="F27:I29"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I39"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="F40:I47"/>
-    <mergeCell ref="B48:B57"/>
-    <mergeCell ref="B58:B66"/>
-    <mergeCell ref="F48:I57"/>
-    <mergeCell ref="F58:I66"/>
-    <mergeCell ref="B67:B75"/>
-    <mergeCell ref="F67:I75"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
     <mergeCell ref="F92:I92"/>
     <mergeCell ref="E30:E34"/>
     <mergeCell ref="E48:E57"/>
@@ -4250,6 +4327,40 @@
     <mergeCell ref="F84:I84"/>
     <mergeCell ref="F85:I85"/>
     <mergeCell ref="F86:I86"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="B48:B57"/>
+    <mergeCell ref="B58:B66"/>
+    <mergeCell ref="F48:I57"/>
+    <mergeCell ref="F58:I66"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="F67:I75"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I39"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B47"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="F40:I47"/>
+    <mergeCell ref="D20:D26"/>
+    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="F20:I26"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="F30:I34"/>
+    <mergeCell ref="F27:I29"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="F6:I12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="F13:I14"/>
+    <mergeCell ref="F15:I17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:I19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -4271,34 +4382,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4343,355 +4454,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="78" t="s">
-        <v>449</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="A1" s="80" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" s="80" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80" t="s">
+        <v>233</v>
+      </c>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A3" s="79" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80" t="s">
+        <v>431</v>
+      </c>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+    </row>
+    <row r="4" spans="1:11" ht="35.25" customHeight="1">
+      <c r="A4" s="79"/>
+      <c r="B4" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>430</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="79"/>
+      <c r="B5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D5" s="80" t="s">
         <v>456</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80" t="s">
+        <v>438</v>
+      </c>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="79"/>
+      <c r="B6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D6" s="80" t="s">
         <v>457</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="D2" s="78" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
+        <v>441</v>
+      </c>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="79"/>
+      <c r="B7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D7" s="80" t="s">
+        <v>458</v>
+      </c>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80" t="s">
+        <v>444</v>
+      </c>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="79"/>
+      <c r="B8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>459</v>
+      </c>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80" t="s">
+        <v>446</v>
+      </c>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="79"/>
+      <c r="B9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="80" t="s">
+        <v>460</v>
+      </c>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80" t="s">
+        <v>448</v>
+      </c>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="79"/>
+      <c r="B10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="80" t="s">
+        <v>452</v>
+      </c>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80" t="s">
+        <v>461</v>
+      </c>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="79"/>
+      <c r="B11" t="s">
+        <v>462</v>
+      </c>
+      <c r="C11" t="s">
+        <v>463</v>
+      </c>
+      <c r="D11" s="80" t="s">
+        <v>464</v>
+      </c>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80" t="s">
+        <v>465</v>
+      </c>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="79"/>
+      <c r="B12" t="s">
+        <v>466</v>
+      </c>
+      <c r="C12" t="s">
+        <v>467</v>
+      </c>
+      <c r="D12" s="80" t="s">
+        <v>468</v>
+      </c>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80" t="s">
+        <v>469</v>
+      </c>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="79"/>
+      <c r="B13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C13" t="s">
+        <v>471</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>472</v>
+      </c>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80" t="s">
+        <v>473</v>
+      </c>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="79"/>
+      <c r="B14" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>475</v>
+      </c>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80" t="s">
         <v>476</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78" t="s">
-        <v>256</v>
-      </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A3" s="42" t="s">
-        <v>455</v>
-      </c>
-      <c r="B3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D3" s="78" t="s">
-        <v>477</v>
-      </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78" t="s">
-        <v>454</v>
-      </c>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-    </row>
-    <row r="4" spans="1:11" ht="35.25" customHeight="1">
-      <c r="A4" s="42"/>
-      <c r="B4" s="80" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="80" t="s">
-        <v>453</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>478</v>
-      </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="79" t="s">
-        <v>458</v>
-      </c>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="42"/>
-      <c r="B5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D5" s="78" t="s">
-        <v>479</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78" t="s">
-        <v>461</v>
-      </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="42"/>
-      <c r="B6" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6" t="s">
-        <v>463</v>
-      </c>
-      <c r="D6" s="78" t="s">
-        <v>480</v>
-      </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78" t="s">
-        <v>464</v>
-      </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="42"/>
-      <c r="B7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C7" t="s">
-        <v>465</v>
-      </c>
-      <c r="D7" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78" t="s">
-        <v>467</v>
-      </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="42"/>
-      <c r="B8" t="s">
-        <v>474</v>
-      </c>
-      <c r="C8" t="s">
-        <v>468</v>
-      </c>
-      <c r="D8" s="78" t="s">
-        <v>482</v>
-      </c>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78" t="s">
-        <v>469</v>
-      </c>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="78"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="42"/>
-      <c r="B9" t="s">
-        <v>473</v>
-      </c>
-      <c r="C9" t="s">
-        <v>470</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>483</v>
-      </c>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78" t="s">
-        <v>471</v>
-      </c>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="42"/>
-      <c r="B10" t="s">
-        <v>472</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>475</v>
-      </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78" t="s">
-        <v>484</v>
-      </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="42"/>
-      <c r="B11" t="s">
-        <v>485</v>
-      </c>
-      <c r="C11" t="s">
-        <v>486</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>487</v>
-      </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78" t="s">
-        <v>488</v>
-      </c>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="42"/>
-      <c r="B12" t="s">
-        <v>489</v>
-      </c>
-      <c r="C12" t="s">
-        <v>490</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>491</v>
-      </c>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78" t="s">
-        <v>492</v>
-      </c>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="42"/>
-      <c r="B13" t="s">
-        <v>493</v>
-      </c>
-      <c r="C13" t="s">
-        <v>494</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>495</v>
-      </c>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78" t="s">
-        <v>496</v>
-      </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="42"/>
-      <c r="B14" t="s">
-        <v>497</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>498</v>
-      </c>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78" t="s">
-        <v>499</v>
-      </c>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="17"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
+      <c r="A17" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="82" t="s">
-        <v>31</v>
+      <c r="A18" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="82"/>
-      <c r="B19" s="82" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="82"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="82"/>
+      <c r="A20" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="G9:K9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4703,14 +4805,23 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
     <mergeCell ref="G3:K3"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="G5:K5"/>
     <mergeCell ref="G6:K6"/>
     <mergeCell ref="G7:K7"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4718,145 +4829,698 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92162386-6B35-48E0-A018-D511D929EC80}">
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.125" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    <row r="1" spans="1:16">
+      <c r="A1" s="69" t="s">
+        <v>486</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>489</v>
+      </c>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69" t="s">
+        <v>490</v>
+      </c>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="69" t="s">
+        <v>12</v>
+      </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>477</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>487</v>
+      </c>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80" t="s">
+        <v>492</v>
+      </c>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="69" t="s">
+        <v>491</v>
+      </c>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="79" t="s">
+        <v>505</v>
+      </c>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="69"/>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>478</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80" t="s">
+        <v>493</v>
+      </c>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="69"/>
       <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>479</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>482</v>
+      </c>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80" t="s">
+        <v>494</v>
+      </c>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="69"/>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>480</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>485</v>
+      </c>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80" t="s">
+        <v>495</v>
+      </c>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="69"/>
       <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80" t="s">
+        <v>496</v>
+      </c>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="69"/>
+      <c r="B9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80" t="s">
+        <v>499</v>
+      </c>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>501</v>
+      </c>
+      <c r="C10" s="80" t="s">
+        <v>502</v>
+      </c>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69" t="s">
+        <v>500</v>
+      </c>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="69"/>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C11" s="80" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="69"/>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="69"/>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="69" t="s">
+        <v>504</v>
+      </c>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>507</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>513</v>
+      </c>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="69" t="s">
+        <v>514</v>
+      </c>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69" t="s">
+        <v>506</v>
+      </c>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="79" t="s">
+        <v>512</v>
+      </c>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="69"/>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>508</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="69" t="s">
+        <v>515</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="69"/>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>511</v>
+      </c>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="69" t="s">
+        <v>509</v>
+      </c>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="69"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="69"/>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="80" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="69" t="s">
+        <v>510</v>
+      </c>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="79" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79" t="s">
+        <v>519</v>
+      </c>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="69"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="69"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="69"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="K29" t="s">
+        <v>483</v>
+      </c>
+      <c r="L29" s="83" t="s">
+        <v>484</v>
+      </c>
+      <c r="M29" s="80" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="L31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
+    <row r="34" spans="3:12">
+      <c r="K34" t="s">
+        <v>42</v>
+      </c>
+      <c r="L34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
+      <c r="K35" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
+      <c r="C37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
+      <c r="C38" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
+      <c r="C39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
+      <c r="C40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:E21"/>
+    <mergeCell ref="J18:L21"/>
+    <mergeCell ref="M18:P21"/>
+    <mergeCell ref="F18:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="J10:L13"/>
+    <mergeCell ref="M10:P13"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="J14:L17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="M14:P17"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="M4:P9"/>
+    <mergeCell ref="J4:L9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+  </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4872,193 +5536,193 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5079,42 +5743,42 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -5122,23 +5786,23 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>0.5</v>
@@ -5146,23 +5810,23 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B11">
         <v>17</v>
@@ -5170,7 +5834,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <v>28</v>
@@ -5178,44 +5842,44 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1">
         <v>60000</v>
@@ -5223,7 +5887,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1">
         <v>81</v>
@@ -5231,7 +5895,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B21" s="1">
         <v>0.12</v>
@@ -5239,7 +5903,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B22" s="1">
         <v>1.2</v>
@@ -5247,23 +5911,23 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1</v>
@@ -5271,37 +5935,37 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B29">
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5311,18 +5975,18 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -5346,22 +6010,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5369,171 +6033,171 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="G3" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="E16" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="F16" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="E17" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -5554,92 +6218,92 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.25">
       <c r="A1" s="10" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="49.5">
       <c r="A3" s="9" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="49.5">
       <c r="A4" s="9" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="33">
       <c r="A5" s="11" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" ht="33">
       <c r="A6" s="9" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" ht="17.25" thickBot="1">
       <c r="A7" s="9" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="33">
       <c r="A8" s="9" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="33">
       <c r="A9" s="9" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="33">
       <c r="A10" s="9" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:5" ht="66.75" thickBot="1">
       <c r="A11" s="12" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B11" s="8"/>
     </row>
@@ -5651,27 +6315,27 @@
     </row>
     <row r="14" spans="1:5" ht="26.25">
       <c r="A14" s="4" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -5690,190 +6354,190 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="78" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="A1" s="80" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="77" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
+      <c r="A2" s="82" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+      <c r="A3" s="82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="A4" s="82" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="77" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
+      <c r="A5" s="82" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="77" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
+      <c r="A6" s="82" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="77"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="77"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="77" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
+      <c r="A9" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
+      <c r="A10" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="77" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
+      <c r="A11" s="82" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="77" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
+      <c r="A12" s="82" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="77" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
+      <c r="A13" s="82" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="77" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="A14" s="82" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
+      <c r="A15" s="82" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="77"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="14" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5884,214 +6548,224 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="79"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="79"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="79"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="79"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="79"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="79"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="79"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="79"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="79"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="79"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="79"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="79"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="79"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="79"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="79"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="79"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="79"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="79"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="79"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="79"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A20:H20"/>
@@ -6104,23 +6778,13 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6139,105 +6803,105 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="B1" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="C9" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/수정된 사양서/프로젝트 사양서.xlsx
+++ b/수정된 사양서/프로젝트 사양서.xlsx
@@ -3,21 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704AFFF3-9349-491C-9449-B025D442787F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3B2CA5-633A-43D6-B7A2-C8DF8C32892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAY-1(한글)" sheetId="10" r:id="rId1"/>
     <sheet name="DAY-2(한글)" sheetId="11" r:id="rId2"/>
     <sheet name="Day-3(한글)" sheetId="12" r:id="rId3"/>
-    <sheet name="Day-3" sheetId="3" r:id="rId4"/>
-    <sheet name="DAY-4" sheetId="4" r:id="rId5"/>
-    <sheet name="DAY-5" sheetId="5" r:id="rId6"/>
-    <sheet name="DAY-6" sheetId="6" r:id="rId7"/>
-    <sheet name="Grounding" sheetId="7" r:id="rId8"/>
-    <sheet name="day-10" sheetId="8" r:id="rId9"/>
-    <sheet name="Bonus Session" sheetId="9" r:id="rId10"/>
+    <sheet name="DAY-4" sheetId="4" r:id="rId4"/>
+    <sheet name="DAY-5" sheetId="5" r:id="rId5"/>
+    <sheet name="DAY-6" sheetId="6" r:id="rId6"/>
+    <sheet name="Grounding" sheetId="7" r:id="rId7"/>
+    <sheet name="day-10" sheetId="8" r:id="rId8"/>
+    <sheet name="Bonus Session" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="524">
   <si>
     <t>12v</t>
   </si>
@@ -81,48 +80,15 @@
     <t>ESD DIODES/TVS DIODES</t>
   </si>
   <si>
-    <t>Leckage Current</t>
-  </si>
-  <si>
-    <t>Standoff voltage</t>
-  </si>
-  <si>
-    <t>Break down voltage</t>
-  </si>
-  <si>
-    <t>Clamping Voltage</t>
-  </si>
-  <si>
-    <t>Paracitic cap</t>
-  </si>
-  <si>
-    <t>XC</t>
-  </si>
-  <si>
-    <t>1/2 PI F C</t>
-  </si>
-  <si>
     <t>FC(High), C(High) Imp (Low)</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
     <t>TX+, TX-, RX+, RX-</t>
   </si>
   <si>
     <t>3.3V</t>
   </si>
   <si>
-    <t>&gt;3.3V</t>
-  </si>
-  <si>
-    <t>ESD3V3D9</t>
-  </si>
-  <si>
-    <t>RJ45 With Mag</t>
-  </si>
-  <si>
     <t>Working Voltage</t>
   </si>
   <si>
@@ -135,30 +101,12 @@
     <t>Magnetics with RJ45</t>
   </si>
   <si>
-    <t>G8X-188S7-BP</t>
-  </si>
-  <si>
     <t>Ferrite Bead</t>
   </si>
   <si>
-    <t>R dc</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>Range of freq</t>
-  </si>
-  <si>
     <t xml:space="preserve">Current </t>
   </si>
   <si>
-    <t>Current of line</t>
-  </si>
-  <si>
-    <t>MPZ1608B471ATA00</t>
-  </si>
-  <si>
     <t>IMP</t>
   </si>
   <si>
@@ -183,9 +131,6 @@
     <t>JTAG</t>
   </si>
   <si>
-    <t>Programming / debugging</t>
-  </si>
-  <si>
     <t>testing (Max processing)</t>
   </si>
   <si>
@@ -213,18 +158,12 @@
     <t>IPC-STD-7351</t>
   </si>
   <si>
-    <t>ICHOP</t>
-  </si>
-  <si>
     <t>3A</t>
   </si>
   <si>
     <t>VREF</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>VOFF</t>
   </si>
   <si>
@@ -237,27 +176,15 @@
     <t>4.8V</t>
   </si>
   <si>
-    <t>Gain</t>
-  </si>
-  <si>
     <t>3.05V</t>
   </si>
   <si>
-    <t>Vout</t>
-  </si>
-  <si>
     <t>r2*vin/(r1+r2)</t>
   </si>
   <si>
-    <t>3r1+3r2=r2*4.8</t>
-  </si>
-  <si>
     <t>r1/r2</t>
   </si>
   <si>
-    <t>1.8/3.3</t>
-  </si>
-  <si>
     <t>r1</t>
   </si>
   <si>
@@ -276,24 +203,9 @@
     <t xml:space="preserve">application Page </t>
   </si>
   <si>
-    <t>BULK CAPS</t>
-  </si>
-  <si>
-    <t>CMIN</t>
-  </si>
-  <si>
     <t>D*(1-D)*IO/ DELV*Fsw</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Vo*100/VIN*eff</t>
-  </si>
-  <si>
-    <t>I0</t>
-  </si>
-  <si>
     <t>7.6A</t>
   </si>
   <si>
@@ -301,15 +213,6 @@
   </si>
   <si>
     <t>12V</t>
-  </si>
-  <si>
-    <t>fsw</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>delv</t>
   </si>
   <si>
     <t>Cmin</t>
@@ -1309,10 +1212,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>STM32V103CBT6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>모델명</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1334,10 +1233,6 @@
   </si>
   <si>
     <t>ADS122C04IPW</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRV8701E</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1510,14 +1405,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>DP838261ERHBR</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CS32L22</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>CIRRUS LOGIC</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1910,6 +1797,169 @@
   <si>
     <t>SWD -&gt; 프로그램, 디버깅, ARM 아키텍쳐, printf 가능
 JTAG -&gt; Test, 독립적, 별도의 아키텍쳐 없음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32F103CBT6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DP83826IRHBR</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS43L22</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRV8701ERGET</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최소 커패시터 용량</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모터 드라이버 IC 설계 사항</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>명칭</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICHOP</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unknown</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>3A</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>50mV</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VOFF시 Typical 전압</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.8V</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chopping 위한 Vref 레벨
+8.2.1.2.3 참고하여 계산</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>내부 레귤레이터
+6.3V 1uF 세라믹 권장</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain(Av)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICHOP위한 내부 증폭값(Rsense)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>20V/V</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정된 전류값 초과시 정지한다
+Vref 필수 - AVDD에서 분압</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vout(Vref 값)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8/3.3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전류(고정)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voff(고정)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Av(고정)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rsense</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SO(Volt)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BULK CAPS 선정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 리플(Delta)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 리플(delv)/민웰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>효율(eff)/민웰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스위칭 주파수(fsw)/민웰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>I0/요구 전류</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.12(peak to peak)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEANWELL RS-100-12 기준</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vo*100/VIN*eff</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스위치(Delta)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-((Vin-효율)/Vout)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1917,6 +1967,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -2539,6 +2592,25 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2554,36 +2626,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2593,72 +2713,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2668,8 +2722,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2686,6 +2739,143 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19668</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C2A3C4B-E08B-4A63-9817-E5EDA7EAD518}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8515350" y="495565"/>
+          <a:ext cx="6477000" cy="1829153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152288</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E41F8E9D-957F-8BFB-7CA8-A68CA49E5742}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8524874" y="2609850"/>
+          <a:ext cx="6572251" cy="895238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>89483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E76B1DB4-D389-6846-0916-6609F12E678C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8467725" y="3771901"/>
+          <a:ext cx="6686550" cy="3023182"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2965,1352 +3155,1386 @@
   <sheetData>
     <row r="2" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="3" spans="2:9">
-      <c r="B3" s="49" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="51"/>
+      <c r="B3" s="76" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="54"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="63"/>
     </row>
     <row r="5" spans="2:9" ht="17.25" thickBot="1">
       <c r="B5" s="29" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
+        <v>203</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="79"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="57" t="s">
-        <v>339</v>
+      <c r="B6" s="80" t="s">
+        <v>307</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="44"/>
+        <v>305</v>
+      </c>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="51"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="41"/>
+      <c r="B7" s="48"/>
       <c r="C7" s="23" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="48"/>
+        <v>306</v>
+      </c>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="53"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="41"/>
+      <c r="B8" s="48"/>
       <c r="C8" s="23" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
+        <v>306</v>
+      </c>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="53"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="41"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="23" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="48"/>
+        <v>313</v>
+      </c>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="53"/>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="41"/>
+      <c r="B10" s="48"/>
       <c r="C10" s="23" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="48"/>
+        <v>315</v>
+      </c>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="53"/>
     </row>
     <row r="11" spans="2:9" ht="33">
-      <c r="B11" s="41"/>
+      <c r="B11" s="48"/>
       <c r="C11" s="23" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="48"/>
+        <v>316</v>
+      </c>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="53"/>
     </row>
     <row r="12" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B12" s="42"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="24" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>354</v>
-      </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="46"/>
+        <v>322</v>
+      </c>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="55"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="57" t="s">
-        <v>336</v>
+      <c r="B13" s="80" t="s">
+        <v>304</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="44"/>
+        <v>378</v>
+      </c>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="51"/>
     </row>
     <row r="14" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B14" s="42"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="24" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="46"/>
+        <v>318</v>
+      </c>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="55"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="40" t="s">
-        <v>238</v>
+      <c r="B15" s="47" t="s">
+        <v>206</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="E15" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="51"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="48"/>
+      <c r="C16" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="41"/>
-      <c r="C16" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>275</v>
-      </c>
       <c r="E16" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
+        <v>321</v>
+      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
     </row>
     <row r="17" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B17" s="42"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="24" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="E17" s="25"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="46"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="55"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="40" t="s">
-        <v>247</v>
+      <c r="B18" s="47" t="s">
+        <v>215</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>252</v>
-      </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
+        <v>218</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="51"/>
     </row>
     <row r="19" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B19" s="42"/>
+      <c r="B19" s="49"/>
       <c r="C19" s="24" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="46"/>
+        <v>219</v>
+      </c>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="55"/>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="26" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>382</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>383</v>
-      </c>
-      <c r="F20" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
+        <v>223</v>
+      </c>
+      <c r="D20" s="67" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>225</v>
+      </c>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="71"/>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="28" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
+        <v>224</v>
+      </c>
+      <c r="D21" s="68"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="73"/>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="28" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
+        <v>226</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="73"/>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="28" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
+        <v>227</v>
+      </c>
+      <c r="D23" s="68"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="28" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="64"/>
+        <v>232</v>
+      </c>
+      <c r="D24" s="68"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="73"/>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="28" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="64"/>
+        <v>234</v>
+      </c>
+      <c r="D25" s="68"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="73"/>
     </row>
     <row r="26" spans="2:9" ht="17.25" thickBot="1">
       <c r="B26" s="27" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="66"/>
+        <v>236</v>
+      </c>
+      <c r="D26" s="69"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="75"/>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="26" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="F27" s="67"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="51"/>
+        <v>378</v>
+      </c>
+      <c r="F27" s="56"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="58"/>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="28" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="F28" s="68"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="70"/>
+        <v>317</v>
+      </c>
+      <c r="F28" s="59"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="60"/>
     </row>
     <row r="29" spans="2:9" ht="17.25" thickBot="1">
       <c r="B29" s="27" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="F29" s="71"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="54"/>
+        <v>317</v>
+      </c>
+      <c r="F29" s="61"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="40" t="s">
-        <v>273</v>
+      <c r="B30" s="47" t="s">
+        <v>241</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D30" s="32">
         <v>24</v>
       </c>
-      <c r="E30" s="75" t="s">
-        <v>413</v>
-      </c>
-      <c r="F30" s="67"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="51"/>
+      <c r="E30" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="F30" s="56"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="58"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="41"/>
+      <c r="B31" s="48"/>
       <c r="C31" s="23" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="70"/>
+        <v>252</v>
+      </c>
+      <c r="E31" s="43"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="60"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="41"/>
+      <c r="B32" s="48"/>
       <c r="C32" s="23" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="D32" s="21">
         <v>128</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="70"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="60"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="41"/>
+      <c r="B33" s="48"/>
       <c r="C33" s="23" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="70"/>
+        <v>247</v>
+      </c>
+      <c r="E33" s="43"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="60"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B34" s="42"/>
+      <c r="B34" s="49"/>
       <c r="C34" s="24" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="E34" s="77"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="54"/>
+        <v>249</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="2:9" ht="17.25" thickBot="1">
       <c r="B35" s="29" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="F35" s="72"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="74"/>
+        <v>378</v>
+      </c>
+      <c r="F35" s="64"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="66"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="40" t="s">
-        <v>285</v>
+      <c r="B36" s="47" t="s">
+        <v>253</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>287</v>
-      </c>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="44"/>
+        <v>254</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="41"/>
+      <c r="B37" s="48"/>
       <c r="C37" s="23" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="47"/>
-      <c r="I37" s="48"/>
+        <v>252</v>
+      </c>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="53"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="41"/>
+      <c r="B38" s="48"/>
       <c r="C38" s="23" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="D38" s="21">
         <f>5000/0.005</f>
         <v>1000000</v>
       </c>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="48"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="53"/>
     </row>
     <row r="39" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B39" s="42"/>
+      <c r="B39" s="49"/>
       <c r="C39" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="55"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="F40" s="56"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="58"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="48"/>
+      <c r="C41" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" s="43"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="60"/>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="48"/>
+      <c r="C42" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E42" s="43"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="60"/>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="48"/>
+      <c r="C43" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" s="43"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="60"/>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="48"/>
+      <c r="C44" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" s="43"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="60"/>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="48"/>
+      <c r="C45" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" s="43"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="60"/>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="48"/>
+      <c r="C46" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" s="43"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="60"/>
+    </row>
+    <row r="47" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B47" s="49"/>
+      <c r="C47" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" s="44"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="62"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="63"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="51"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="48"/>
+      <c r="C49" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="E49" s="43"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="53"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="48"/>
+      <c r="C50" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E50" s="43"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="53"/>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="48"/>
+      <c r="C51" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="E51" s="43"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="53"/>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="48"/>
+      <c r="C52" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E52" s="43"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="53"/>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" s="48"/>
+      <c r="C53" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="E53" s="43"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="53"/>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" s="48"/>
+      <c r="C54" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E54" s="43"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="53"/>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="48"/>
+      <c r="C55" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E55" s="43"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="53"/>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="48"/>
+      <c r="C56" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E56" s="43"/>
+      <c r="F56" s="52"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="53"/>
+    </row>
+    <row r="57" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B57" s="49"/>
+      <c r="C57" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E57" s="44"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="55"/>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D58" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="46"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="40" t="s">
-        <v>385</v>
-      </c>
-      <c r="C40" s="19" t="s">
+      <c r="E58" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="F58" s="56"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="58"/>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" s="48"/>
+      <c r="C59" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="E40" s="75" t="s">
-        <v>414</v>
-      </c>
-      <c r="F40" s="67"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="51"/>
-    </row>
-    <row r="41" spans="2:9">
-      <c r="B41" s="41"/>
-      <c r="C41" s="23" t="s">
+      <c r="D59" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="E41" s="76"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="70"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="41"/>
-      <c r="C42" s="23" t="s">
+      <c r="E59" s="43"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="60"/>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" s="48"/>
+      <c r="C60" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D60" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="E42" s="76"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="70"/>
-    </row>
-    <row r="43" spans="2:9">
-      <c r="B43" s="41"/>
-      <c r="C43" s="23" t="s">
+      <c r="E60" s="43"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="60"/>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="48"/>
+      <c r="C61" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="E43" s="76"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="70"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="41"/>
-      <c r="C44" s="23" t="s">
+      <c r="E61" s="43"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="60"/>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" s="48"/>
+      <c r="C62" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D62" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="E44" s="76"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="70"/>
-    </row>
-    <row r="45" spans="2:9">
-      <c r="B45" s="41"/>
-      <c r="C45" s="23" t="s">
+      <c r="E62" s="43"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="60"/>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="B63" s="48"/>
+      <c r="C63" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="E45" s="76"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="70"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="41"/>
-      <c r="C46" s="23" t="s">
+      <c r="D63" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E63" s="43"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="60"/>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" s="48"/>
+      <c r="C64" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="E46" s="76"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="70"/>
-    </row>
-    <row r="47" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B47" s="42"/>
-      <c r="C47" s="24" t="s">
+      <c r="D64" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E64" s="43"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="60"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="48"/>
+      <c r="C65" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="D47" s="34" t="s">
-        <v>345</v>
-      </c>
-      <c r="E47" s="77"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="54"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="40" t="s">
+      <c r="D65" s="21"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="60"/>
+    </row>
+    <row r="66" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B66" s="49"/>
+      <c r="C66" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="C48" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="E48" s="78" t="s">
-        <v>412</v>
-      </c>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="44"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="41"/>
-      <c r="C49" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="E49" s="76"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="48"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="41"/>
-      <c r="C50" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E50" s="76"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="48"/>
-    </row>
-    <row r="51" spans="2:9">
-      <c r="B51" s="41"/>
-      <c r="C51" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="E51" s="76"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="48"/>
-    </row>
-    <row r="52" spans="2:9">
-      <c r="B52" s="41"/>
-      <c r="C52" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="E52" s="76"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
-      <c r="I52" s="48"/>
-    </row>
-    <row r="53" spans="2:9">
-      <c r="B53" s="41"/>
-      <c r="C53" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="E53" s="76"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="48"/>
-    </row>
-    <row r="54" spans="2:9">
-      <c r="B54" s="41"/>
-      <c r="C54" s="23" t="s">
+      <c r="D66" s="34"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="61"/>
+      <c r="G66" s="62"/>
+      <c r="H66" s="62"/>
+      <c r="I66" s="63"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="45"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="58"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="B68" s="48"/>
+      <c r="C68" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E68" s="43"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="60"/>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" s="48"/>
+      <c r="C69" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E69" s="43"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="60"/>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="B70" s="48"/>
+      <c r="C70" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="E70" s="43"/>
+      <c r="F70" s="59"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="60"/>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="B71" s="48"/>
+      <c r="C71" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="E71" s="43"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="60"/>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="B72" s="48"/>
+      <c r="C72" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="E72" s="43"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="60"/>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="48"/>
+      <c r="C73" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="E73" s="43"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="60"/>
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="48"/>
+      <c r="C74" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D74" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="E54" s="76"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
-      <c r="I54" s="48"/>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="41"/>
-      <c r="C55" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="E55" s="76"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="48"/>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" s="41"/>
-      <c r="C56" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>318</v>
-      </c>
-      <c r="E56" s="76"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="47"/>
-      <c r="I56" s="48"/>
-    </row>
-    <row r="57" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B57" s="42"/>
-      <c r="C57" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>345</v>
-      </c>
-      <c r="E57" s="77"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="46"/>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" s="40" t="s">
-        <v>321</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="E58" s="78" t="s">
-        <v>412</v>
-      </c>
-      <c r="F58" s="67"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="51"/>
-    </row>
-    <row r="59" spans="2:9">
-      <c r="B59" s="41"/>
-      <c r="C59" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E59" s="76"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="70"/>
-    </row>
-    <row r="60" spans="2:9">
-      <c r="B60" s="41"/>
-      <c r="C60" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="E60" s="76"/>
-      <c r="F60" s="68"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="70"/>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="B61" s="41"/>
-      <c r="C61" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="E61" s="76"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="70"/>
-    </row>
-    <row r="62" spans="2:9">
-      <c r="B62" s="41"/>
-      <c r="C62" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="E62" s="76"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="70"/>
-    </row>
-    <row r="63" spans="2:9">
-      <c r="B63" s="41"/>
-      <c r="C63" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="E63" s="76"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="70"/>
-    </row>
-    <row r="64" spans="2:9">
-      <c r="B64" s="41"/>
-      <c r="C64" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="E64" s="76"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="70"/>
-    </row>
-    <row r="65" spans="2:9">
-      <c r="B65" s="41"/>
-      <c r="C65" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="D65" s="21"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="70"/>
-    </row>
-    <row r="66" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B66" s="42"/>
-      <c r="C66" s="24" t="s">
+      <c r="E74" s="43"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="60"/>
+    </row>
+    <row r="75" spans="2:9" ht="17.25" thickBot="1">
+      <c r="B75" s="49"/>
+      <c r="C75" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="D66" s="34"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="71"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="53"/>
-      <c r="I66" s="54"/>
-    </row>
-    <row r="67" spans="2:9">
-      <c r="B67" s="40" t="s">
-        <v>355</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="D67" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="E67" s="78"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="50"/>
-      <c r="H67" s="50"/>
-      <c r="I67" s="51"/>
-    </row>
-    <row r="68" spans="2:9">
-      <c r="B68" s="41"/>
-      <c r="C68" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="76"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="70"/>
-    </row>
-    <row r="69" spans="2:9">
-      <c r="B69" s="41"/>
-      <c r="C69" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E69" s="76"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="70"/>
-    </row>
-    <row r="70" spans="2:9">
-      <c r="B70" s="41"/>
-      <c r="C70" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="E70" s="76"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="69"/>
-      <c r="I70" s="70"/>
-    </row>
-    <row r="71" spans="2:9">
-      <c r="B71" s="41"/>
-      <c r="C71" s="23" t="s">
-        <v>362</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="E71" s="76"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="69"/>
-      <c r="I71" s="70"/>
-    </row>
-    <row r="72" spans="2:9">
-      <c r="B72" s="41"/>
-      <c r="C72" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="E72" s="76"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="70"/>
-    </row>
-    <row r="73" spans="2:9">
-      <c r="B73" s="41"/>
-      <c r="C73" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="E73" s="76"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="69"/>
-      <c r="H73" s="69"/>
-      <c r="I73" s="70"/>
-    </row>
-    <row r="74" spans="2:9">
-      <c r="B74" s="41"/>
-      <c r="C74" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="E74" s="76"/>
-      <c r="F74" s="68"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="70"/>
-    </row>
-    <row r="75" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B75" s="42"/>
-      <c r="C75" s="24" t="s">
-        <v>367</v>
-      </c>
       <c r="D75" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E75" s="77"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="53"/>
-      <c r="H75" s="53"/>
-      <c r="I75" s="54"/>
+        <v>336</v>
+      </c>
+      <c r="E75" s="44"/>
+      <c r="F75" s="61"/>
+      <c r="G75" s="62"/>
+      <c r="H75" s="62"/>
+      <c r="I75" s="63"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="36" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="F77" s="69" t="s">
-        <v>402</v>
-      </c>
-      <c r="G77" s="69"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="69"/>
+        <v>357</v>
+      </c>
+      <c r="F77" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="41"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="16" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="F78" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="G78" s="69"/>
-      <c r="H78" s="69"/>
-      <c r="I78" s="69"/>
+        <v>358</v>
+      </c>
+      <c r="F78" s="41" t="s">
+        <v>359</v>
+      </c>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="16" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>372</v>
+        <v>484</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="F79" s="69" t="s">
-        <v>395</v>
-      </c>
-      <c r="G79" s="69"/>
-      <c r="H79" s="69"/>
-      <c r="I79" s="69"/>
+        <v>360</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>361</v>
+      </c>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="16" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>421</v>
+        <v>485</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="F80" s="69" t="s">
-        <v>397</v>
-      </c>
-      <c r="G80" s="69"/>
-      <c r="H80" s="69"/>
-      <c r="I80" s="69"/>
+        <v>362</v>
+      </c>
+      <c r="F80" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="16" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="F81" s="69" t="s">
-        <v>400</v>
-      </c>
-      <c r="G81" s="69"/>
-      <c r="H81" s="69"/>
-      <c r="I81" s="69"/>
+        <v>365</v>
+      </c>
+      <c r="F81" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="16" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="F82" s="79" t="s">
-        <v>401</v>
-      </c>
-      <c r="G82" s="69"/>
-      <c r="H82" s="69"/>
-      <c r="I82" s="69"/>
+        <v>369</v>
+      </c>
+      <c r="F82" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="16" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="F83" s="69" t="s">
-        <v>404</v>
-      </c>
-      <c r="G83" s="69"/>
-      <c r="H83" s="69"/>
-      <c r="I83" s="69"/>
+        <v>371</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>370</v>
+      </c>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="16" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>409</v>
-      </c>
-      <c r="F84" s="69" t="s">
-        <v>410</v>
-      </c>
-      <c r="G84" s="69"/>
-      <c r="H84" s="69"/>
-      <c r="I84" s="69"/>
+        <v>375</v>
+      </c>
+      <c r="F84" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="16" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>422</v>
+        <v>486</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="F85" s="69" t="s">
-        <v>424</v>
-      </c>
-      <c r="G85" s="69"/>
-      <c r="H85" s="69"/>
-      <c r="I85" s="69"/>
+        <v>389</v>
+      </c>
+      <c r="F85" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="41"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="16" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="F86" s="69" t="s">
-        <v>417</v>
-      </c>
-      <c r="G86" s="69"/>
-      <c r="H86" s="69"/>
-      <c r="I86" s="69"/>
+        <v>374</v>
+      </c>
+      <c r="F86" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="16" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="F87" s="69" t="s">
-        <v>420</v>
-      </c>
-      <c r="G87" s="69"/>
-      <c r="H87" s="69"/>
-      <c r="I87" s="69"/>
+        <v>374</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>386</v>
+      </c>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
     </row>
     <row r="88" spans="2:9">
-      <c r="F88" s="69"/>
-      <c r="G88" s="69"/>
-      <c r="H88" s="69"/>
-      <c r="I88" s="69"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="41"/>
+      <c r="I88" s="41"/>
     </row>
     <row r="89" spans="2:9">
-      <c r="F89" s="69"/>
-      <c r="G89" s="69"/>
-      <c r="H89" s="69"/>
-      <c r="I89" s="69"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="41"/>
+      <c r="H89" s="41"/>
+      <c r="I89" s="41"/>
     </row>
     <row r="90" spans="2:9">
-      <c r="F90" s="69"/>
-      <c r="G90" s="69"/>
-      <c r="H90" s="69"/>
-      <c r="I90" s="69"/>
+      <c r="F90" s="41"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="41"/>
+      <c r="I90" s="41"/>
     </row>
     <row r="91" spans="2:9">
-      <c r="F91" s="69"/>
-      <c r="G91" s="69"/>
-      <c r="H91" s="69"/>
-      <c r="I91" s="69"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="41"/>
+      <c r="I91" s="41"/>
     </row>
     <row r="92" spans="2:9">
-      <c r="F92" s="69"/>
-      <c r="G92" s="69"/>
-      <c r="H92" s="69"/>
-      <c r="I92" s="69"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
+      <c r="H92" s="41"/>
+      <c r="I92" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="F13:I14"/>
+    <mergeCell ref="F15:I17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:I19"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="F6:I12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D20:D26"/>
+    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="F20:I26"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="F30:I34"/>
+    <mergeCell ref="F27:I29"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I39"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B47"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="F40:I47"/>
+    <mergeCell ref="B48:B57"/>
+    <mergeCell ref="B58:B66"/>
+    <mergeCell ref="F48:I57"/>
+    <mergeCell ref="F58:I66"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="F67:I75"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
     <mergeCell ref="F92:I92"/>
     <mergeCell ref="E30:E34"/>
     <mergeCell ref="E48:E57"/>
@@ -4327,40 +4551,6 @@
     <mergeCell ref="F84:I84"/>
     <mergeCell ref="F85:I85"/>
     <mergeCell ref="F86:I86"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="B48:B57"/>
-    <mergeCell ref="B58:B66"/>
-    <mergeCell ref="F48:I57"/>
-    <mergeCell ref="F58:I66"/>
-    <mergeCell ref="B67:B75"/>
-    <mergeCell ref="F67:I75"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I39"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="F40:I47"/>
-    <mergeCell ref="D20:D26"/>
-    <mergeCell ref="E20:E26"/>
-    <mergeCell ref="F20:I26"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="F30:I34"/>
-    <mergeCell ref="F27:I29"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="F6:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="F13:I14"/>
-    <mergeCell ref="F15:I17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:I19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -4368,78 +4558,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4454,307 +4572,307 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="80" t="s">
-        <v>426</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
+      <c r="A1" s="81" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="18" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="C2" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="D2" s="81" t="s">
+        <v>417</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A3" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>418</v>
+      </c>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81" t="s">
+        <v>395</v>
+      </c>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+    </row>
+    <row r="4" spans="1:11" ht="35.25" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>419</v>
+      </c>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="82" t="s">
+        <v>399</v>
+      </c>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="46"/>
+      <c r="B5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="81" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81" t="s">
         <v>402</v>
       </c>
-      <c r="D2" s="80" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80" t="s">
-        <v>233</v>
-      </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A3" s="79" t="s">
-        <v>432</v>
-      </c>
-      <c r="B3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80" t="s">
-        <v>431</v>
-      </c>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-    </row>
-    <row r="4" spans="1:11" ht="35.25" customHeight="1">
-      <c r="A4" s="79"/>
-      <c r="B4" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>430</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>455</v>
-      </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="81" t="s">
-        <v>435</v>
-      </c>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="79"/>
-      <c r="B5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C5" t="s">
-        <v>437</v>
-      </c>
-      <c r="D5" s="80" t="s">
-        <v>456</v>
-      </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80" t="s">
-        <v>438</v>
-      </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="79"/>
+      <c r="A6" s="46"/>
       <c r="B6" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="C6" t="s">
-        <v>440</v>
-      </c>
-      <c r="D6" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80" t="s">
-        <v>441</v>
-      </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+        <v>404</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>421</v>
+      </c>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81" t="s">
+        <v>405</v>
+      </c>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="79"/>
+      <c r="A7" s="46"/>
       <c r="B7" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
-        <v>442</v>
-      </c>
-      <c r="D7" s="80" t="s">
-        <v>458</v>
-      </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80" t="s">
-        <v>444</v>
-      </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
+        <v>406</v>
+      </c>
+      <c r="D7" s="81" t="s">
+        <v>422</v>
+      </c>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81" t="s">
+        <v>408</v>
+      </c>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="79"/>
+      <c r="A8" s="46"/>
       <c r="B8" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D8" s="80" t="s">
-        <v>459</v>
-      </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80" t="s">
-        <v>446</v>
-      </c>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
+        <v>409</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81" t="s">
+        <v>410</v>
+      </c>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="79"/>
+      <c r="A9" s="46"/>
       <c r="B9" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="C9" t="s">
-        <v>447</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80" t="s">
-        <v>448</v>
-      </c>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
+        <v>411</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81" t="s">
+        <v>412</v>
+      </c>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="79"/>
+      <c r="A10" s="46"/>
       <c r="B10" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="80" t="s">
-        <v>452</v>
-      </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80" t="s">
-        <v>461</v>
-      </c>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
+      <c r="D10" s="81" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81" t="s">
+        <v>425</v>
+      </c>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="79"/>
+      <c r="A11" s="46"/>
       <c r="B11" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="C11" t="s">
-        <v>463</v>
-      </c>
-      <c r="D11" s="80" t="s">
-        <v>464</v>
-      </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80" t="s">
-        <v>465</v>
-      </c>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
+        <v>427</v>
+      </c>
+      <c r="D11" s="81" t="s">
+        <v>428</v>
+      </c>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="79"/>
+      <c r="A12" s="46"/>
       <c r="B12" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="C12" t="s">
-        <v>467</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>468</v>
-      </c>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80" t="s">
-        <v>469</v>
-      </c>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
+        <v>431</v>
+      </c>
+      <c r="D12" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="79"/>
+      <c r="A13" s="46"/>
       <c r="B13" t="s">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="C13" t="s">
-        <v>471</v>
-      </c>
-      <c r="D13" s="80" t="s">
-        <v>472</v>
-      </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80" t="s">
-        <v>473</v>
-      </c>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
+        <v>435</v>
+      </c>
+      <c r="D13" s="81" t="s">
+        <v>436</v>
+      </c>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81" t="s">
+        <v>437</v>
+      </c>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="79"/>
+      <c r="A14" s="46"/>
       <c r="B14" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="80" t="s">
-        <v>475</v>
-      </c>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80" t="s">
-        <v>476</v>
-      </c>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
+      <c r="D14" s="81" t="s">
+        <v>439</v>
+      </c>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81" t="s">
+        <v>440</v>
+      </c>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="17"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="38" t="s">
@@ -4792,6 +4910,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="G8:K8"/>
     <mergeCell ref="G9:K9"/>
     <mergeCell ref="D10:F10"/>
@@ -4808,20 +4940,6 @@
     <mergeCell ref="G3:K3"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="G5:K5"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4839,647 +4957,626 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="69" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
+      <c r="A1" s="41" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="69"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>488</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>489</v>
-      </c>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69" t="s">
-        <v>490</v>
-      </c>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41" t="s">
+        <v>454</v>
+      </c>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="41" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="81" t="s">
+        <v>451</v>
+      </c>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81" t="s">
+        <v>456</v>
+      </c>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="41" t="s">
+        <v>455</v>
+      </c>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="41"/>
+      <c r="B5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81" t="s">
+        <v>457</v>
+      </c>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="41"/>
+      <c r="B6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81" t="s">
+        <v>458</v>
+      </c>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="41"/>
+      <c r="B7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81" t="s">
+        <v>459</v>
+      </c>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="41"/>
+      <c r="B8" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81" t="s">
+        <v>460</v>
+      </c>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="41"/>
+      <c r="B9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81" t="s">
+        <v>463</v>
+      </c>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>466</v>
+      </c>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41" t="s">
+        <v>464</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="41"/>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="41"/>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="41"/>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>467</v>
+      </c>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="41" t="s">
+        <v>468</v>
+      </c>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>477</v>
       </c>
-      <c r="C4" s="80" t="s">
-        <v>487</v>
-      </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80" t="s">
-        <v>492</v>
-      </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="69" t="s">
-        <v>491</v>
-      </c>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="79" t="s">
-        <v>505</v>
-      </c>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="69"/>
-      <c r="B5" t="s">
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="41" t="s">
         <v>478</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="41"/>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>472</v>
+      </c>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="41" t="s">
+        <v>479</v>
+      </c>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="41"/>
+      <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80" t="s">
-        <v>493</v>
-      </c>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="69"/>
-      <c r="B6" t="s">
-        <v>479</v>
-      </c>
-      <c r="C6" s="80" t="s">
-        <v>482</v>
-      </c>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80" t="s">
-        <v>494</v>
-      </c>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="69"/>
-      <c r="B7" t="s">
+      <c r="C16" s="81" t="s">
+        <v>475</v>
+      </c>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="41" t="s">
+        <v>473</v>
+      </c>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="41"/>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="81" t="s">
         <v>480</v>
       </c>
-      <c r="C7" s="80" t="s">
-        <v>485</v>
-      </c>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80" t="s">
-        <v>495</v>
-      </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="69"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="69"/>
-      <c r="B8" t="s">
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="41" t="s">
+        <v>474</v>
+      </c>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="46" t="s">
         <v>481</v>
       </c>
-      <c r="C8" s="80" t="s">
-        <v>329</v>
-      </c>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80" t="s">
-        <v>496</v>
-      </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="69"/>
-      <c r="B9" t="s">
-        <v>497</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80" t="s">
-        <v>499</v>
-      </c>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>501</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>502</v>
-      </c>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69" t="s">
-        <v>500</v>
-      </c>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="69"/>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>345</v>
-      </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="69"/>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="80" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="69"/>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>503</v>
-      </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="69" t="s">
-        <v>504</v>
-      </c>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>507</v>
-      </c>
-      <c r="C14" s="80" t="s">
-        <v>513</v>
-      </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="69" t="s">
-        <v>514</v>
-      </c>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69" t="s">
-        <v>506</v>
-      </c>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="79" t="s">
-        <v>512</v>
-      </c>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="69"/>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="80" t="s">
-        <v>508</v>
-      </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="69" t="s">
-        <v>515</v>
-      </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="69"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="69"/>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="80" t="s">
-        <v>511</v>
-      </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="69" t="s">
-        <v>509</v>
-      </c>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="69"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="69"/>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="80" t="s">
-        <v>516</v>
-      </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="69" t="s">
-        <v>510</v>
-      </c>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="79" t="s">
-        <v>517</v>
-      </c>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="79" t="s">
-        <v>519</v>
-      </c>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="80"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="80"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="69"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="81"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="69"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="69"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
+        <v>36</v>
+      </c>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
+        <v>38</v>
+      </c>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
     </row>
     <row r="29" spans="1:16">
       <c r="K29" t="s">
-        <v>483</v>
-      </c>
-      <c r="L29" s="83" t="s">
-        <v>484</v>
-      </c>
-      <c r="M29" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
+        <v>447</v>
+      </c>
+      <c r="L29" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="M29" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81"/>
     </row>
     <row r="31" spans="1:16">
       <c r="L31" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="3:12">
       <c r="K34" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="3:12">
       <c r="K35" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="3:12">
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="3:12">
       <c r="C38" s="1" t="s">
-        <v>518</v>
+        <v>482</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="3:12">
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="3:12">
       <c r="C40" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:E21"/>
-    <mergeCell ref="J18:L21"/>
-    <mergeCell ref="M18:P21"/>
-    <mergeCell ref="F18:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="M4:P9"/>
+    <mergeCell ref="J4:L9"/>
     <mergeCell ref="J10:L13"/>
     <mergeCell ref="M10:P13"/>
     <mergeCell ref="A4:A9"/>
@@ -5490,33 +5587,30 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="M4:P9"/>
-    <mergeCell ref="J4:L9"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:E21"/>
+    <mergeCell ref="J18:L21"/>
+    <mergeCell ref="M18:P21"/>
+    <mergeCell ref="F18:I21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5525,477 +5619,507 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
-    <col min="3" max="3" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="41" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="81" t="s">
+        <v>490</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>494</v>
+      </c>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="41" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>496</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>498</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="81" t="s">
+        <v>502</v>
+      </c>
+      <c r="B12" s="81"/>
+      <c r="C12" s="16">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>504</v>
+      </c>
+      <c r="E12" s="81" t="s">
+        <v>503</v>
+      </c>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="41" t="s">
+        <v>506</v>
+      </c>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>507</v>
+      </c>
+      <c r="D15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>513</v>
+      </c>
+      <c r="B22" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C24" t="s">
+        <v>523</v>
+      </c>
+      <c r="D24" s="84"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B27" s="1">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B28" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.2345680000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+      <c r="J37" t="s">
+        <v>508</v>
+      </c>
+      <c r="K37" t="s">
+        <v>509</v>
+      </c>
+      <c r="L37" t="s">
+        <v>510</v>
+      </c>
+      <c r="M37" t="s">
+        <v>511</v>
+      </c>
+      <c r="O37" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38">
+        <v>0.05</v>
+      </c>
+      <c r="L38">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" t="s">
-        <v>56</v>
+      <c r="M38">
+        <v>0.05</v>
+      </c>
+      <c r="O38">
+        <f>J38*L38*M38+K38</f>
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:I14"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:I7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:I9"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:I5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A1:O2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:I3"/>
+  </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="1">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="1">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29">
-        <v>52</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -6010,22 +6134,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="G1" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6033,171 +6157,171 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66">
       <c r="A3" s="2" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="E16" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="E17" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -6206,7 +6330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -6218,92 +6342,92 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.25">
       <c r="A1" s="10" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="49.5">
       <c r="A3" s="9" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="49.5">
       <c r="A4" s="9" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="33">
       <c r="A5" s="11" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" ht="33">
       <c r="A6" s="9" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" ht="17.25" thickBot="1">
       <c r="A7" s="9" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="33">
       <c r="A8" s="9" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="33">
       <c r="A9" s="9" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="33">
       <c r="A10" s="9" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:5" ht="66.75" thickBot="1">
       <c r="A11" s="12" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B11" s="8"/>
     </row>
@@ -6315,27 +6439,27 @@
     </row>
     <row r="14" spans="1:5" ht="26.25">
       <c r="A14" s="4" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -6348,196 +6472,196 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="80" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
+      <c r="A1" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="82" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
+      <c r="A2" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="82" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="A3" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
+      <c r="A4" s="83" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
+      <c r="A5" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="82" t="s">
-        <v>183</v>
-      </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
+      <c r="A6" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="82"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="82"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="82" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
+      <c r="A9" s="83" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
+      <c r="A10" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="82" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
+      <c r="A11" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="82" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
+      <c r="A12" s="83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="82" t="s">
-        <v>188</v>
-      </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
+      <c r="A13" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="82" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
+      <c r="A14" s="83" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
+      <c r="A15" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="82"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="14" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -6548,207 +6672,231 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="81"/>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="81"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="81"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="81"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="81"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="81"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="82"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="81"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="81"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="81"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="81"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
+      <c r="A27" s="82"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="81"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="81"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="81"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="81"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
+      <c r="A31" s="82"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="81"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
+      <c r="A32" s="82"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="81"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
+      <c r="A33" s="82"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="81"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
+      <c r="A34" s="82"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="81"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="81"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
+      <c r="A36" s="82"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="81"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:H2"/>
@@ -6761,37 +6909,13 @@
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A36:H36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -6803,109 +6927,181 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C1" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="C9" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/수정된 사양서/프로젝트 사양서.xlsx
+++ b/수정된 사양서/프로젝트 사양서.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3B2CA5-633A-43D6-B7A2-C8DF8C32892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A941443-CA20-41CE-BA50-874433CD0D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAY-1(한글)" sheetId="10" r:id="rId1"/>
     <sheet name="DAY-2(한글)" sheetId="11" r:id="rId2"/>
     <sheet name="Day-3(한글)" sheetId="12" r:id="rId3"/>
-    <sheet name="DAY-4" sheetId="4" r:id="rId4"/>
-    <sheet name="DAY-5" sheetId="5" r:id="rId5"/>
+    <sheet name="DAY-4(한글)" sheetId="4" r:id="rId4"/>
+    <sheet name="DAY-5(한글)" sheetId="5" r:id="rId5"/>
     <sheet name="DAY-6" sheetId="6" r:id="rId6"/>
     <sheet name="Grounding" sheetId="7" r:id="rId7"/>
     <sheet name="day-10" sheetId="8" r:id="rId8"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="527">
   <si>
     <t>12v</t>
   </si>
@@ -1237,10 +1237,6 @@
   </si>
   <si>
     <t>DMHT6016LFJ</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DAC + 마이크</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1960,6 +1956,22 @@
   </si>
   <si>
     <t>1-((Vin-효율)/Vout)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DAC </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMP34DT05</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HCLGA 4LD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEMS audio sensor omnidirectional digital microphone</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1968,7 +1980,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -2593,9 +2605,112 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2611,108 +2726,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2722,7 +2735,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3141,7 +3153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DC7827-D177-44C1-93C8-C705450FADE1}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I93"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20.5" style="17" bestFit="1" customWidth="1"/>
@@ -3155,26 +3167,26 @@
   <sheetData>
     <row r="2" spans="2:9" ht="17.25" thickBot="1"/>
     <row r="3" spans="2:9">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B4" s="77"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="63"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="2:9" ht="17.25" thickBot="1">
       <c r="B5" s="29" t="s">
@@ -3189,15 +3201,15 @@
       <c r="E5" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="59" t="s">
         <v>307</v>
       </c>
       <c r="C6" s="19" t="s">
@@ -3209,13 +3221,13 @@
       <c r="E6" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="48"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="23" t="s">
         <v>194</v>
       </c>
@@ -3225,13 +3237,13 @@
       <c r="E7" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="53"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="50"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="48"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="23" t="s">
         <v>195</v>
       </c>
@@ -3241,13 +3253,13 @@
       <c r="E8" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="53"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="48"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="23" t="s">
         <v>196</v>
       </c>
@@ -3257,13 +3269,13 @@
       <c r="E9" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="53"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="50"/>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="48"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="23" t="s">
         <v>197</v>
       </c>
@@ -3273,13 +3285,13 @@
       <c r="E10" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="53"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="50"/>
     </row>
     <row r="11" spans="2:9" ht="33">
-      <c r="B11" s="48"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="23" t="s">
         <v>198</v>
       </c>
@@ -3289,13 +3301,13 @@
       <c r="E11" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="53"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="50"/>
     </row>
     <row r="12" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B12" s="49"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="24" t="s">
         <v>199</v>
       </c>
@@ -3305,13 +3317,13 @@
       <c r="E12" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="55"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="59" t="s">
         <v>304</v>
       </c>
       <c r="C13" s="19" t="s">
@@ -3321,15 +3333,15 @@
         <v>209</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="51"/>
+        <v>377</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46"/>
     </row>
     <row r="14" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B14" s="49"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="24" t="s">
         <v>205</v>
       </c>
@@ -3339,13 +3351,13 @@
       <c r="E14" s="25" t="s">
         <v>318</v>
       </c>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="55"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="48"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="42" t="s">
         <v>206</v>
       </c>
       <c r="C15" s="19" t="s">
@@ -3357,13 +3369,13 @@
       <c r="E15" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="48"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="23" t="s">
         <v>207</v>
       </c>
@@ -3373,13 +3385,13 @@
       <c r="E16" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="50"/>
     </row>
     <row r="17" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B17" s="49"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="24" t="s">
         <v>212</v>
       </c>
@@ -3387,13 +3399,13 @@
         <v>213</v>
       </c>
       <c r="E17" s="25"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="55"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="42" t="s">
         <v>215</v>
       </c>
       <c r="C18" s="19" t="s">
@@ -3402,29 +3414,29 @@
       <c r="D18" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46"/>
     </row>
     <row r="19" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B19" s="49"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="24" t="s">
         <v>217</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="26" t="s">
@@ -3433,18 +3445,18 @@
       <c r="C20" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="E20" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="E20" s="50" t="s">
-        <v>349</v>
-      </c>
-      <c r="F20" s="70" t="s">
+      <c r="F20" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="28" t="s">
@@ -3453,12 +3465,12 @@
       <c r="C21" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="73"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="28" t="s">
@@ -3467,12 +3479,12 @@
       <c r="C22" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="73"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="28" t="s">
@@ -3481,12 +3493,12 @@
       <c r="C23" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="66"/>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="28" t="s">
@@ -3495,12 +3507,12 @@
       <c r="C24" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="73"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="28" t="s">
@@ -3509,12 +3521,12 @@
       <c r="C25" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="68"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="73"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="2:9" ht="17.25" thickBot="1">
       <c r="B26" s="27" t="s">
@@ -3523,12 +3535,12 @@
       <c r="C26" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="75"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="68"/>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="26" t="s">
@@ -3539,12 +3551,12 @@
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="F27" s="56"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="58"/>
+        <v>377</v>
+      </c>
+      <c r="F27" s="69"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="28" t="s">
@@ -3554,15 +3566,15 @@
         <v>313</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="F28" s="59"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="60"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="72"/>
     </row>
     <row r="29" spans="2:9" ht="17.25" thickBot="1">
       <c r="B29" s="27" t="s">
@@ -3572,18 +3584,18 @@
         <v>313</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E29" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="F29" s="61"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="63"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="42" t="s">
         <v>241</v>
       </c>
       <c r="C30" s="19" t="s">
@@ -3592,69 +3604,69 @@
       <c r="D30" s="32">
         <v>24</v>
       </c>
-      <c r="E30" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="F30" s="56"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="58"/>
+      <c r="E30" s="77" t="s">
+        <v>378</v>
+      </c>
+      <c r="F30" s="69"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="48"/>
+      <c r="B31" s="43"/>
       <c r="C31" s="23" t="s">
         <v>244</v>
       </c>
       <c r="D31" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="60"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="72"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="48"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="23" t="s">
         <v>245</v>
       </c>
       <c r="D32" s="21">
         <v>128</v>
       </c>
-      <c r="E32" s="43"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="60"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="72"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="48"/>
+      <c r="B33" s="43"/>
       <c r="C33" s="23" t="s">
         <v>246</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="E33" s="43"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="60"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="72"/>
     </row>
     <row r="34" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B34" s="49"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="24" t="s">
         <v>248</v>
       </c>
       <c r="D34" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="63"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="56"/>
     </row>
     <row r="35" spans="2:9" ht="17.25" thickBot="1">
       <c r="B35" s="29" t="s">
@@ -3667,47 +3679,47 @@
         <v>252</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="F35" s="64"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="66"/>
+        <v>377</v>
+      </c>
+      <c r="F35" s="74"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="76"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="42" t="s">
         <v>253</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D36" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="51"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="48"/>
+      <c r="B37" s="43"/>
       <c r="C37" s="23" t="s">
         <v>256</v>
       </c>
       <c r="D37" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="53"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="50"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="48"/>
+      <c r="B38" s="43"/>
       <c r="C38" s="23" t="s">
         <v>257</v>
       </c>
@@ -3715,29 +3727,29 @@
         <f>5000/0.005</f>
         <v>1000000</v>
       </c>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="53"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="50"/>
     </row>
     <row r="39" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B39" s="49"/>
+      <c r="B39" s="44"/>
       <c r="C39" s="24" t="s">
         <v>258</v>
       </c>
       <c r="D39" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="55"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="48"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="47" t="s">
-        <v>351</v>
+      <c r="B40" s="42" t="s">
+        <v>350</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>260</v>
@@ -3745,258 +3757,258 @@
       <c r="D40" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="E40" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="F40" s="56"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
+      <c r="E40" s="77" t="s">
+        <v>379</v>
+      </c>
+      <c r="F40" s="69"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="53"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="48"/>
+      <c r="B41" s="43"/>
       <c r="C41" s="23" t="s">
         <v>261</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="E41" s="43"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="60"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="72"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="48"/>
+      <c r="B42" s="43"/>
       <c r="C42" s="23" t="s">
         <v>262</v>
       </c>
       <c r="D42" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="E42" s="43"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="60"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="48"/>
+      <c r="B43" s="43"/>
       <c r="C43" s="23" t="s">
         <v>265</v>
       </c>
       <c r="D43" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="E43" s="43"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="60"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="72"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="48"/>
+      <c r="B44" s="43"/>
       <c r="C44" s="23" t="s">
         <v>267</v>
       </c>
       <c r="D44" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="60"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="72"/>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="48"/>
+      <c r="B45" s="43"/>
       <c r="C45" s="23" t="s">
         <v>268</v>
       </c>
       <c r="D45" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="E45" s="43"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="60"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="48"/>
+      <c r="B46" s="43"/>
       <c r="C46" s="23" t="s">
         <v>269</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="E46" s="43"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="60"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="72"/>
     </row>
     <row r="47" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B47" s="49"/>
+      <c r="B47" s="44"/>
       <c r="C47" s="24" t="s">
         <v>270</v>
       </c>
       <c r="D47" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="E47" s="44"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="62"/>
-      <c r="I47" s="63"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="56"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="42" t="s">
         <v>271</v>
       </c>
       <c r="C48" s="19" t="s">
         <v>272</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="E48" s="45" t="s">
-        <v>378</v>
-      </c>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="51"/>
+        <v>354</v>
+      </c>
+      <c r="E48" s="80" t="s">
+        <v>377</v>
+      </c>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="46"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="48"/>
+      <c r="B49" s="43"/>
       <c r="C49" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D49" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="E49" s="43"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="53"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="50"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="48"/>
+      <c r="B50" s="43"/>
       <c r="C50" s="23" t="s">
         <v>274</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="E50" s="43"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="53"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="50"/>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="48"/>
+      <c r="B51" s="43"/>
       <c r="C51" s="23" t="s">
         <v>276</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="E51" s="43"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="53"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="50"/>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="48"/>
+      <c r="B52" s="43"/>
       <c r="C52" s="23" t="s">
         <v>278</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="E52" s="43"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="53"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="50"/>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="48"/>
+      <c r="B53" s="43"/>
       <c r="C53" s="23" t="s">
         <v>284</v>
       </c>
       <c r="D53" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="E53" s="43"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
-      <c r="I53" s="53"/>
+      <c r="E53" s="78"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="50"/>
     </row>
     <row r="54" spans="2:9">
-      <c r="B54" s="48"/>
+      <c r="B54" s="43"/>
       <c r="C54" s="23" t="s">
         <v>281</v>
       </c>
       <c r="D54" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="E54" s="43"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="53"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="50"/>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="48"/>
+      <c r="B55" s="43"/>
       <c r="C55" s="23" t="s">
         <v>288</v>
       </c>
       <c r="D55" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="E55" s="43"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="53"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="50"/>
     </row>
     <row r="56" spans="2:9">
-      <c r="B56" s="48"/>
+      <c r="B56" s="43"/>
       <c r="C56" s="23" t="s">
         <v>285</v>
       </c>
       <c r="D56" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="E56" s="43"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="53"/>
+      <c r="E56" s="78"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="50"/>
     </row>
     <row r="57" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B57" s="49"/>
+      <c r="B57" s="44"/>
       <c r="C57" s="24" t="s">
         <v>287</v>
       </c>
       <c r="D57" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="E57" s="44"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
-      <c r="H57" s="54"/>
-      <c r="I57" s="55"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="48"/>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="47" t="s">
+      <c r="B58" s="42" t="s">
         <v>289</v>
       </c>
       <c r="C58" s="19" t="s">
@@ -4005,124 +4017,124 @@
       <c r="D58" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="E58" s="45" t="s">
-        <v>378</v>
-      </c>
-      <c r="F58" s="56"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="58"/>
+      <c r="E58" s="80" t="s">
+        <v>377</v>
+      </c>
+      <c r="F58" s="69"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="53"/>
     </row>
     <row r="59" spans="2:9">
-      <c r="B59" s="48"/>
+      <c r="B59" s="43"/>
       <c r="C59" s="23" t="s">
         <v>292</v>
       </c>
       <c r="D59" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="E59" s="43"/>
-      <c r="F59" s="59"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="60"/>
+      <c r="E59" s="78"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="72"/>
     </row>
     <row r="60" spans="2:9">
-      <c r="B60" s="48"/>
+      <c r="B60" s="43"/>
       <c r="C60" s="23" t="s">
         <v>294</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="E60" s="43"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="60"/>
+      <c r="E60" s="78"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="71"/>
+      <c r="I60" s="72"/>
     </row>
     <row r="61" spans="2:9">
-      <c r="B61" s="48"/>
+      <c r="B61" s="43"/>
       <c r="C61" s="23" t="s">
         <v>296</v>
       </c>
       <c r="D61" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="E61" s="43"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="60"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="72"/>
     </row>
     <row r="62" spans="2:9">
-      <c r="B62" s="48"/>
+      <c r="B62" s="43"/>
       <c r="C62" s="23" t="s">
         <v>298</v>
       </c>
       <c r="D62" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="E62" s="43"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="60"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="72"/>
     </row>
     <row r="63" spans="2:9">
-      <c r="B63" s="48"/>
+      <c r="B63" s="43"/>
       <c r="C63" s="23" t="s">
         <v>300</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="E63" s="43"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="60"/>
+        <v>353</v>
+      </c>
+      <c r="E63" s="78"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="71"/>
+      <c r="H63" s="71"/>
+      <c r="I63" s="72"/>
     </row>
     <row r="64" spans="2:9">
-      <c r="B64" s="48"/>
+      <c r="B64" s="43"/>
       <c r="C64" s="23" t="s">
         <v>301</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E64" s="43"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="60"/>
+        <v>352</v>
+      </c>
+      <c r="E64" s="78"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="72"/>
     </row>
     <row r="65" spans="2:9">
-      <c r="B65" s="48"/>
+      <c r="B65" s="43"/>
       <c r="C65" s="23" t="s">
         <v>302</v>
       </c>
       <c r="D65" s="21"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="60"/>
+      <c r="E65" s="78"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="72"/>
     </row>
     <row r="66" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B66" s="49"/>
+      <c r="B66" s="44"/>
       <c r="C66" s="24" t="s">
         <v>303</v>
       </c>
       <c r="D66" s="34"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="62"/>
-      <c r="H66" s="62"/>
-      <c r="I66" s="63"/>
+      <c r="E66" s="79"/>
+      <c r="F66" s="73"/>
+      <c r="G66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="56"/>
     </row>
     <row r="67" spans="2:9">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="42" t="s">
         <v>323</v>
       </c>
       <c r="C67" s="19" t="s">
@@ -4131,123 +4143,123 @@
       <c r="D67" s="32" t="s">
         <v>324</v>
       </c>
-      <c r="E67" s="45"/>
-      <c r="F67" s="56"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="58"/>
+      <c r="E67" s="80"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="52"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="53"/>
     </row>
     <row r="68" spans="2:9">
-      <c r="B68" s="48"/>
+      <c r="B68" s="43"/>
       <c r="C68" s="23" t="s">
         <v>325</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="E68" s="43"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="60"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="72"/>
     </row>
     <row r="69" spans="2:9">
-      <c r="B69" s="48"/>
+      <c r="B69" s="43"/>
       <c r="C69" s="23" t="s">
         <v>327</v>
       </c>
       <c r="D69" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="E69" s="43"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="60"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="72"/>
     </row>
     <row r="70" spans="2:9">
-      <c r="B70" s="48"/>
+      <c r="B70" s="43"/>
       <c r="C70" s="23" t="s">
         <v>329</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="E70" s="43"/>
-      <c r="F70" s="59"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="60"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="71"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="72"/>
     </row>
     <row r="71" spans="2:9">
-      <c r="B71" s="48"/>
+      <c r="B71" s="43"/>
       <c r="C71" s="23" t="s">
         <v>330</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E71" s="43"/>
-      <c r="F71" s="59"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="41"/>
-      <c r="I71" s="60"/>
+        <v>380</v>
+      </c>
+      <c r="E71" s="78"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="71"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="72"/>
     </row>
     <row r="72" spans="2:9">
-      <c r="B72" s="48"/>
+      <c r="B72" s="43"/>
       <c r="C72" s="23" t="s">
         <v>331</v>
       </c>
       <c r="D72" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="E72" s="43"/>
-      <c r="F72" s="59"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="60"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="70"/>
+      <c r="G72" s="71"/>
+      <c r="H72" s="71"/>
+      <c r="I72" s="72"/>
     </row>
     <row r="73" spans="2:9">
-      <c r="B73" s="48"/>
+      <c r="B73" s="43"/>
       <c r="C73" s="23" t="s">
         <v>333</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="E73" s="43"/>
-      <c r="F73" s="59"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="60"/>
+        <v>381</v>
+      </c>
+      <c r="E73" s="78"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="72"/>
     </row>
     <row r="74" spans="2:9">
-      <c r="B74" s="48"/>
+      <c r="B74" s="43"/>
       <c r="C74" s="23" t="s">
         <v>334</v>
       </c>
       <c r="D74" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="E74" s="43"/>
-      <c r="F74" s="59"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="41"/>
-      <c r="I74" s="60"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="71"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="72"/>
     </row>
     <row r="75" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B75" s="49"/>
+      <c r="B75" s="44"/>
       <c r="C75" s="24" t="s">
         <v>335</v>
       </c>
       <c r="D75" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="E75" s="44"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="62"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="63"/>
+      <c r="E75" s="79"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="56"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="36" t="s">
@@ -4260,14 +4272,14 @@
         <v>200</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="F77" s="41" t="s">
-        <v>368</v>
-      </c>
-      <c r="G77" s="41"/>
-      <c r="H77" s="41"/>
-      <c r="I77" s="41"/>
+        <v>356</v>
+      </c>
+      <c r="F77" s="71" t="s">
+        <v>367</v>
+      </c>
+      <c r="G77" s="71"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="71"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="16" t="s">
@@ -4280,54 +4292,54 @@
         <v>341</v>
       </c>
       <c r="E78" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="F78" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="F78" s="41" t="s">
-        <v>359</v>
-      </c>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="71"/>
+      <c r="I78" s="71"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="16" t="s">
         <v>339</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>341</v>
       </c>
       <c r="E79" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="F79" s="71" t="s">
         <v>360</v>
       </c>
-      <c r="F79" s="41" t="s">
-        <v>361</v>
-      </c>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="41"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="71"/>
+      <c r="I79" s="71"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="16" t="s">
         <v>215</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E80" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="F80" s="71" t="s">
         <v>362</v>
       </c>
-      <c r="F80" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="71"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="16" t="s">
@@ -4337,17 +4349,17 @@
         <v>343</v>
       </c>
       <c r="D81" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E81" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="E81" s="16" t="s">
+      <c r="F81" s="71" t="s">
         <v>365</v>
       </c>
-      <c r="F81" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="41"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="71"/>
+      <c r="I81" s="71"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="16" t="s">
@@ -4357,37 +4369,37 @@
         <v>345</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="F82" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="G82" s="41"/>
-      <c r="H82" s="41"/>
-      <c r="I82" s="41"/>
+        <v>368</v>
+      </c>
+      <c r="F82" s="81" t="s">
+        <v>366</v>
+      </c>
+      <c r="G82" s="71"/>
+      <c r="H82" s="71"/>
+      <c r="I82" s="71"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="16" t="s">
         <v>271</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="F83" s="41" t="s">
         <v>370</v>
       </c>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41"/>
-      <c r="I83" s="41"/>
+      <c r="F83" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="G83" s="71"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="71"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="16" t="s">
@@ -4397,160 +4409,181 @@
         <v>346</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E84" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="F84" s="71" t="s">
         <v>375</v>
       </c>
-      <c r="F84" s="41" t="s">
-        <v>376</v>
-      </c>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41"/>
-      <c r="I84" s="41"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="71"/>
+      <c r="I84" s="71"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="16" t="s">
-        <v>347</v>
+        <v>523</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D85" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="F85" s="71" t="s">
         <v>387</v>
       </c>
-      <c r="E85" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="F85" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
+      <c r="G85" s="71"/>
+      <c r="H85" s="71"/>
+      <c r="I85" s="71"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="16" t="s">
-        <v>373</v>
+        <v>333</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>313</v>
+        <v>524</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="F86" s="41" t="s">
-        <v>383</v>
-      </c>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41"/>
-      <c r="I86" s="41"/>
+        <v>525</v>
+      </c>
+      <c r="F86" s="71" t="s">
+        <v>526</v>
+      </c>
+      <c r="G86" s="71"/>
+      <c r="H86" s="71"/>
+      <c r="I86" s="71"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="F87" s="71" t="s">
+        <v>382</v>
+      </c>
+      <c r="G87" s="71"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="71"/>
+    </row>
+    <row r="88" spans="2:9">
+      <c r="B88" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="C88" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="D88" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="F88" s="71" t="s">
         <v>385</v>
       </c>
-      <c r="D87" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="E87" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="F87" s="41" t="s">
-        <v>386</v>
-      </c>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="41"/>
-    </row>
-    <row r="88" spans="2:9">
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="41"/>
-      <c r="I88" s="41"/>
+      <c r="G88" s="71"/>
+      <c r="H88" s="71"/>
+      <c r="I88" s="71"/>
     </row>
     <row r="89" spans="2:9">
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="41"/>
-      <c r="I89" s="41"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="71"/>
+      <c r="I89" s="71"/>
     </row>
     <row r="90" spans="2:9">
-      <c r="F90" s="41"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="41"/>
-      <c r="I90" s="41"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
     </row>
     <row r="91" spans="2:9">
-      <c r="F91" s="41"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="41"/>
-      <c r="I91" s="41"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="71"/>
+      <c r="H91" s="71"/>
+      <c r="I91" s="71"/>
     </row>
     <row r="92" spans="2:9">
-      <c r="F92" s="41"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="41"/>
-      <c r="I92" s="41"/>
+      <c r="F92" s="71"/>
+      <c r="G92" s="71"/>
+      <c r="H92" s="71"/>
+      <c r="I92" s="71"/>
+    </row>
+    <row r="93" spans="2:9">
+      <c r="F93" s="71"/>
+      <c r="G93" s="71"/>
+      <c r="H93" s="71"/>
+      <c r="I93" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
+    <mergeCell ref="F86:I86"/>
+    <mergeCell ref="F93:I93"/>
+    <mergeCell ref="E30:E34"/>
+    <mergeCell ref="E48:E57"/>
+    <mergeCell ref="E40:E47"/>
+    <mergeCell ref="E58:E66"/>
+    <mergeCell ref="E67:E75"/>
+    <mergeCell ref="F88:I88"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="F90:I90"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="F92:I92"/>
+    <mergeCell ref="F82:I82"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="F84:I84"/>
+    <mergeCell ref="F85:I85"/>
+    <mergeCell ref="F87:I87"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="B48:B57"/>
+    <mergeCell ref="B58:B66"/>
+    <mergeCell ref="F48:I57"/>
+    <mergeCell ref="F58:I66"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="F67:I75"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I39"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B47"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="F40:I47"/>
+    <mergeCell ref="D20:D26"/>
+    <mergeCell ref="E20:E26"/>
+    <mergeCell ref="F20:I26"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="F30:I34"/>
+    <mergeCell ref="F27:I29"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="F6:I12"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="F13:I14"/>
     <mergeCell ref="F15:I17"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:I19"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="F6:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D20:D26"/>
-    <mergeCell ref="E20:E26"/>
-    <mergeCell ref="F20:I26"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="F30:I34"/>
-    <mergeCell ref="F27:I29"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I39"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="F40:I47"/>
-    <mergeCell ref="B48:B57"/>
-    <mergeCell ref="B58:B66"/>
-    <mergeCell ref="F48:I57"/>
-    <mergeCell ref="F58:I66"/>
-    <mergeCell ref="B67:B75"/>
-    <mergeCell ref="F67:I75"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="F92:I92"/>
-    <mergeCell ref="E30:E34"/>
-    <mergeCell ref="E48:E57"/>
-    <mergeCell ref="E40:E47"/>
-    <mergeCell ref="E58:E66"/>
-    <mergeCell ref="E67:E75"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="F89:I89"/>
-    <mergeCell ref="F90:I90"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="F82:I82"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="F84:I84"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="F86:I86"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -4572,307 +4605,307 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="81" t="s">
-        <v>390</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
+      <c r="A1" s="82" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>416</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" customHeight="1">
+      <c r="A3" s="81" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D3" s="82" t="s">
+        <v>417</v>
+      </c>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82" t="s">
+        <v>394</v>
+      </c>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+    </row>
+    <row r="4" spans="1:11" ht="35.25" customHeight="1">
+      <c r="A4" s="81"/>
+      <c r="B4" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="83" t="s">
         <v>398</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="D2" s="81" t="s">
-        <v>417</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A3" s="46" t="s">
-        <v>396</v>
-      </c>
-      <c r="B3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" t="s">
-        <v>392</v>
-      </c>
-      <c r="D3" s="81" t="s">
-        <v>418</v>
-      </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81" t="s">
-        <v>395</v>
-      </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-    </row>
-    <row r="4" spans="1:11" ht="35.25" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="D4" s="41" t="s">
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="81"/>
+      <c r="B5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="82" t="s">
         <v>419</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="82" t="s">
-        <v>399</v>
-      </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="46"/>
-      <c r="B5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82" t="s">
         <v>401</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="81"/>
+      <c r="B6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="82" t="s">
         <v>420</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81" t="s">
-        <v>402</v>
-      </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="46"/>
-      <c r="B6" t="s">
-        <v>403</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82" t="s">
         <v>404</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="81"/>
+      <c r="B7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D7" s="82" t="s">
         <v>421</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81" t="s">
-        <v>405</v>
-      </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="46"/>
-      <c r="B7" t="s">
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82" t="s">
         <v>407</v>
       </c>
-      <c r="C7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D7" s="81" t="s">
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="81"/>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="82" t="s">
         <v>422</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81" t="s">
-        <v>408</v>
-      </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="46"/>
-      <c r="B8" t="s">
-        <v>415</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82" t="s">
         <v>409</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="81"/>
+      <c r="B9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="82" t="s">
         <v>423</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81" t="s">
-        <v>410</v>
-      </c>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="46"/>
-      <c r="B9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82" t="s">
         <v>411</v>
       </c>
-      <c r="D9" s="81" t="s">
-        <v>424</v>
-      </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81" t="s">
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="81"/>
+      <c r="B10" t="s">
         <v>412</v>
-      </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="46"/>
-      <c r="B10" t="s">
-        <v>413</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="81" t="s">
-        <v>416</v>
-      </c>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81" t="s">
+      <c r="D10" s="82" t="s">
+        <v>415</v>
+      </c>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82" t="s">
+        <v>424</v>
+      </c>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="81"/>
+      <c r="B11" t="s">
         <v>425</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="46"/>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>426</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="82" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="81" t="s">
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82" t="s">
         <v>428</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81" t="s">
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="81"/>
+      <c r="B12" t="s">
         <v>429</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="46"/>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>430</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="82" t="s">
         <v>431</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82" t="s">
         <v>432</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81" t="s">
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="81"/>
+      <c r="B13" t="s">
         <v>433</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="46"/>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>434</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="82" t="s">
         <v>435</v>
       </c>
-      <c r="D13" s="81" t="s">
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82" t="s">
         <v>436</v>
       </c>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81" t="s">
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="81"/>
+      <c r="B14" t="s">
         <v>437</v>
-      </c>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="46"/>
-      <c r="B14" t="s">
-        <v>438</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="81" t="s">
+      <c r="D14" s="82" t="s">
+        <v>438</v>
+      </c>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82" t="s">
         <v>439</v>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81" t="s">
-        <v>440</v>
-      </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="17"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="38" t="s">
@@ -4910,23 +4943,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="D10:F10"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="D2:F2"/>
@@ -4940,6 +4956,23 @@
     <mergeCell ref="G3:K3"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="G5:K5"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4957,512 +4990,512 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="41" t="s">
-        <v>450</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
+      <c r="A1" s="71" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="C3" s="71" t="s">
         <v>452</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71" t="s">
         <v>453</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41" t="s">
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
+        <v>455</v>
+      </c>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="71" t="s">
         <v>454</v>
       </c>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="81" t="s">
+        <v>468</v>
+      </c>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="71"/>
+      <c r="B5" t="s">
         <v>441</v>
       </c>
-      <c r="C4" s="81" t="s">
-        <v>451</v>
-      </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81" t="s">
+      <c r="C5" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82" t="s">
         <v>456</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="41" t="s">
-        <v>455</v>
-      </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="46" t="s">
-        <v>469</v>
-      </c>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="41"/>
-      <c r="B5" t="s">
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="71"/>
+      <c r="B6" t="s">
         <v>442</v>
       </c>
-      <c r="C5" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81" t="s">
+      <c r="C6" s="82" t="s">
+        <v>445</v>
+      </c>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82" t="s">
         <v>457</v>
       </c>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="41"/>
-      <c r="B6" t="s">
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="71"/>
+      <c r="B7" t="s">
         <v>443</v>
       </c>
-      <c r="C6" s="81" t="s">
-        <v>446</v>
-      </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81" t="s">
+      <c r="C7" s="82" t="s">
+        <v>448</v>
+      </c>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82" t="s">
         <v>458</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="41"/>
-      <c r="B7" t="s">
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="71"/>
+      <c r="B8" t="s">
         <v>444</v>
       </c>
-      <c r="C7" s="81" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81" t="s">
+      <c r="C8" s="82" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82" t="s">
         <v>459</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="41"/>
-      <c r="B8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>297</v>
-      </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81" t="s">
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="71"/>
+      <c r="B9" t="s">
         <v>460</v>
       </c>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="41"/>
-      <c r="B9" t="s">
+      <c r="C9" s="82" t="s">
         <v>461</v>
       </c>
-      <c r="C9" s="81" t="s">
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82" t="s">
         <v>462</v>
       </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81" t="s">
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>465</v>
+      </c>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71" t="s">
         <v>463</v>
       </c>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C10" s="81" t="s">
-        <v>466</v>
-      </c>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="41"/>
+      <c r="A11" s="71"/>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="41"/>
+      <c r="A12" s="71"/>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="41"/>
+      <c r="A13" s="71"/>
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="82" t="s">
+        <v>466</v>
+      </c>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="71" t="s">
         <v>467</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="41" t="s">
-        <v>468</v>
-      </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="71" t="s">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>471</v>
-      </c>
-      <c r="C14" s="81" t="s">
+        <v>470</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>476</v>
+      </c>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="71" t="s">
         <v>477</v>
       </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="41" t="s">
-        <v>478</v>
-      </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41" t="s">
-        <v>470</v>
-      </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71" t="s">
+        <v>469</v>
+      </c>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="81" t="s">
+        <v>475</v>
+      </c>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="41"/>
+      <c r="A15" s="71"/>
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="81" t="s">
-        <v>472</v>
-      </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="41" t="s">
-        <v>479</v>
-      </c>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
+      <c r="C15" s="82" t="s">
+        <v>471</v>
+      </c>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="71" t="s">
+        <v>478</v>
+      </c>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="41"/>
+      <c r="A16" s="71"/>
       <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="81" t="s">
-        <v>475</v>
-      </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="41" t="s">
-        <v>473</v>
-      </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
+      <c r="C16" s="82" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="71" t="s">
+        <v>472</v>
+      </c>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="41"/>
+      <c r="A17" s="71"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="82" t="s">
+        <v>479</v>
+      </c>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="71" t="s">
+        <v>473</v>
+      </c>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="81" t="s">
         <v>480</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="41" t="s">
-        <v>474</v>
-      </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>481</v>
-      </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="81" t="s">
+        <v>482</v>
+      </c>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="82"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="82"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="81"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="82"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="82"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="81"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="82"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="82"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
+      <c r="A21" s="71"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="82"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="82"/>
+      <c r="M21" s="82"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
@@ -5471,10 +5504,10 @@
       <c r="B26" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
@@ -5483,23 +5516,23 @@
       <c r="B27" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
     </row>
     <row r="29" spans="1:16">
       <c r="K29" t="s">
+        <v>446</v>
+      </c>
+      <c r="L29" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="L29" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="M29" s="81" t="s">
+      <c r="M29" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="82"/>
     </row>
     <row r="31" spans="1:16">
       <c r="L31" t="s">
@@ -5532,7 +5565,7 @@
     </row>
     <row r="38" spans="3:12">
       <c r="C38" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>30</v>
@@ -5556,6 +5589,47 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="J18:L21"/>
+    <mergeCell ref="M18:P21"/>
+    <mergeCell ref="F18:I21"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:E21"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="J14:L17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="M14:P17"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="M4:P9"/>
+    <mergeCell ref="J4:L9"/>
+    <mergeCell ref="J10:L13"/>
+    <mergeCell ref="M10:P13"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
@@ -5566,51 +5640,10 @@
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F8:I8"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="M3:P3"/>
-    <mergeCell ref="M4:P9"/>
-    <mergeCell ref="J4:L9"/>
-    <mergeCell ref="J10:L13"/>
-    <mergeCell ref="M10:P13"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="J14:L17"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="M14:P17"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:E21"/>
-    <mergeCell ref="J18:L21"/>
-    <mergeCell ref="M18:P21"/>
-    <mergeCell ref="F18:I21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5630,59 +5663,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="71" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="82" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="81" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="E3" s="81" t="s">
-        <v>494</v>
-      </c>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="E3" s="82" t="s">
+        <v>493</v>
+      </c>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
       <c r="J3" s="18"/>
       <c r="K3" s="18"/>
       <c r="L3" s="18"/>
@@ -5691,176 +5724,176 @@
       <c r="O3" s="18"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="41" t="s">
-        <v>493</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="71" t="s">
+        <v>492</v>
+      </c>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="71" t="s">
+        <v>495</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>504</v>
+      </c>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71" t="s">
+        <v>494</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>499</v>
+      </c>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="71" t="s">
         <v>496</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>505</v>
-      </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41" t="s">
-        <v>495</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="46" t="s">
+      <c r="E8" s="71" t="s">
+        <v>497</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="81" t="s">
         <v>500</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>497</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>498</v>
-      </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>499</v>
-      </c>
-      <c r="E10" s="46" t="s">
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="71"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="82" t="s">
         <v>501</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="81" t="s">
-        <v>502</v>
-      </c>
-      <c r="B12" s="81"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="16">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>504</v>
-      </c>
-      <c r="E12" s="81" t="s">
         <v>503</v>
       </c>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="E12" s="82" t="s">
+        <v>502</v>
+      </c>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="41" t="s">
-        <v>506</v>
-      </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41" t="s">
+      <c r="A13" s="71" t="s">
+        <v>505</v>
+      </c>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D15">
         <v>0.5</v>
@@ -5900,15 +5933,15 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>54</v>
@@ -5916,19 +5949,19 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C24" t="s">
         <v>522</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="C24" t="s">
-        <v>523</v>
-      </c>
-      <c r="D24" s="84"/>
+      <c r="D24" s="41"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>55</v>
@@ -5944,7 +5977,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B27" s="1">
         <v>60000</v>
@@ -5952,7 +5985,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B28" s="1">
         <v>81</v>
@@ -5960,15 +5993,15 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B30" s="1">
         <v>1.2345680000000001</v>
@@ -6022,19 +6055,19 @@
         <v>66</v>
       </c>
       <c r="J37" t="s">
+        <v>507</v>
+      </c>
+      <c r="K37" t="s">
         <v>508</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>509</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>510</v>
       </c>
-      <c r="M37" t="s">
+      <c r="O37" t="s">
         <v>511</v>
-      </c>
-      <c r="O37" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -6087,11 +6120,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:I11"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:O2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:I5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="C6:C7"/>
     <mergeCell ref="A13:B14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
@@ -6103,15 +6140,11 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:I9"/>
     <mergeCell ref="E12:I12"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:I5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A1:O2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:I11"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6478,186 +6511,186 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="83"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
+      <c r="A7" s="84"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
+      <c r="A8" s="84"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="84" t="s">
         <v>158</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="83"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="14" t="s">
@@ -6672,214 +6705,224 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="82"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="82"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="82"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
+      <c r="A21" s="83"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="82"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
+      <c r="A22" s="83"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="82"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
+      <c r="A23" s="83"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="82"/>
-      <c r="B24" s="82"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
+      <c r="A24" s="83"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="82"/>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="82"/>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="82"/>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="82"/>
-      <c r="H27" s="82"/>
+      <c r="A27" s="83"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="82"/>
-      <c r="B28" s="82"/>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
+      <c r="A28" s="83"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="82"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82"/>
+      <c r="A29" s="83"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="82"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="A30" s="83"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="82"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
+      <c r="A31" s="83"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="82"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="82"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
+      <c r="A33" s="83"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="82"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="82"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="82"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="82"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
+      <c r="A35" s="83"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="82"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
+      <c r="A36" s="83"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="82"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="82"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
+      <c r="A37" s="83"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A20:H20"/>
@@ -6892,23 +6935,13 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
